--- a/input/products.xlsx
+++ b/input/products.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="47">
   <si>
     <t>url</t>
   </si>
@@ -37,13 +37,10 @@
     <t>done</t>
   </si>
   <si>
-    <t>2026-09-11T10:23:45.793Z</t>
+    <t>2026-09-11T10:42:37.654Z</t>
   </si>
   <si>
     <t>https://tatacliq.com/melange-by-lifestyle-pink-embroidered-viscose-rayon-regular-fit-kurta/p-mp000000031960160</t>
-  </si>
-  <si>
-    <t>pending</t>
   </si>
   <si>
     <t>https://tatacliq.com/libas-womens-green-straight-fit-floral-cotton-kurta/p-mp000000031601124</t>
@@ -584,316 +581,433 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>14</v>
       </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>15</v>
       </c>
-      <c r="C9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>16</v>
       </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>17</v>
       </c>
-      <c r="C11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="C12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>18</v>
       </c>
-      <c r="C12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="C13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>19</v>
       </c>
-      <c r="C13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="C14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>20</v>
       </c>
-      <c r="C14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>21</v>
       </c>
-      <c r="C15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="C16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>22</v>
       </c>
-      <c r="C16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="C17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>23</v>
       </c>
-      <c r="C17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="C18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>24</v>
       </c>
-      <c r="C18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="C19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>25</v>
       </c>
-      <c r="C19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="C20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>26</v>
       </c>
-      <c r="C20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="C21" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>27</v>
       </c>
-      <c r="C21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="C22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>28</v>
       </c>
-      <c r="C22" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="C23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>29</v>
       </c>
-      <c r="C23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="C24" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>30</v>
       </c>
-      <c r="C24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="C25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>31</v>
       </c>
-      <c r="C25" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="C26" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>32</v>
       </c>
-      <c r="C26" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="C27" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>33</v>
       </c>
-      <c r="C27" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="C28" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>34</v>
       </c>
-      <c r="C28" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="C29" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>35</v>
       </c>
-      <c r="C29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="C30" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>36</v>
       </c>
-      <c r="C30" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="C31" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>37</v>
       </c>
-      <c r="C31" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="C32" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>38</v>
       </c>
-      <c r="C32" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="C33" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>39</v>
       </c>
-      <c r="C33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="C34" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>40</v>
       </c>
-      <c r="C34" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="C35" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>41</v>
       </c>
-      <c r="C35" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="C36" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>42</v>
       </c>
-      <c r="C36" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="C37" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>43</v>
       </c>
-      <c r="C37" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="C38" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>44</v>
       </c>
-      <c r="C38" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="C39" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>45</v>
       </c>
-      <c r="C39" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="C40" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>46</v>
       </c>
-      <c r="C40" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>47</v>
-      </c>
       <c r="C41" t="s">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="D41" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">

--- a/input/products.xlsx
+++ b/input/products.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="49">
   <si>
     <t>url</t>
   </si>
@@ -31,143 +31,154 @@
     <t>error</t>
   </si>
   <si>
-    <t>https://tatacliq.com/rangmanch-by-pantaloons-calypso-coral-embroidered-regular-fit-kurta/p-mp000000032018703</t>
+    <t>https://tatacliq.com/koskii-rani-pink-zari-saree/p-mp000000030180975</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/soch-womens-orange-regular-fit-bandhani-viscose-saree/p-mp000000031768720</t>
   </si>
   <si>
     <t>done</t>
   </si>
   <si>
-    <t>2026-09-11T10:42:37.654Z</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/melange-by-lifestyle-pink-embroidered-viscose-rayon-regular-fit-kurta/p-mp000000031960160</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/libas-womens-green-straight-fit-floral-cotton-kurta/p-mp000000031601124</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/taneira-purple-embroidered-viscose-kurta/p-mp000000031978183</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/house-of-chikankari-fuchsia-solid-long-kurta/p-mp000000032070207</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/libas-off-white-abstract-kimono-sleeves-aline-kurti/p-mp000000031111936</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/zuba-by-westside-light-green-floral-printed-aline-kurta/p-mp000000031724243</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/w-pink-printed-straight-kurta/p-mp000000018835986</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/rangmanch-by-pantaloons-maroon-floral-print-casual-kurta/p-mp000000032018655</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/biba-black-printed-kurti/p-mp000000025144803</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/libas-blue-straight-fit-embroidered-kurta/p-mp000000030729354</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/libas-pink-chiffon-printed-kurta/p-mp000000031396260</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/libas-purple-floral-motif-embroidered-panelled-straight-kurta-with-pocket/p-mp000000031111801</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/sabhyata-sky-blue-regular-fit-embroidered-kurta/p-mp000000032087497</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/libas-blue-straight-fit-floral-print-kurta/p-mp000000031117687</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/utsa-by-westside-indigo-floral-printed-cottonblend-aline-kurta/p-mp000000031486324</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/diza-by-westside-offwhite-embroidered-tunic/p-mp000000031486445</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/soch-green-printed-straight-fit-kurta/p-mp000000031961904</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/house-of-chikankari-black-straight-fit-embroidered-kurta/p-mp000000031705563</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/rangmanch-by-pantaloons-yellow-regular-fit-printed-kurta/p-mp000000029122751</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/biba-orange-cotton-straight-fit-kurta/p-mp000000030801930</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/libas-womens-black-straight-fit-embellished-kurta/p-mp000000031601283</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/taneira-dark-blue-kurta/p-mp000000026386762</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/libas-womens-maroon-straight-fit-striped-cotton-blend-kurta/p-mp000000031600971</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/utsa-by-westside-red-geometric-embroidered-cottonblend-aline-kurta/p-mp000000031948085</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/zuba-by-westside-offwhite-floral-embroidered-silk-chanderi-aline-kurta/p-mp000000031724274</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/diza-by-westside-red-floral-printed-aline-kurta/p-mp000000031724175</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/w-for-woman-navy-blue-metallic-embroidered-straight-kurta/p-mp000000031230281</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/varanga-blue-cotton-geometric-kurta/p-mp000000031250259</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/w-mustard-rayonviscose-embroidered-kurti/p-mp000000029084140</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/daali-blue-regular-fit-embroidered-kurta/p-mp000000028267934</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/daali-white-regular-fit-embroidered-kurta/p-mp000000027869066</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/rangmanch-by-pantaloons-fuchsia-purple-regular-fit-embroidered-kurta/p-mp000000031635976</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/soch-blue-floral-cotton-crop-top/p-mp000000031871079</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/utsa-by-westside-pink-floral-pattern-cotton-aline-kurta/p-mp000000031765894</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/gerua-by-libas-yellow-straight-fit-striped-kurta/p-mp000000031117704</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/diza-by-westside-red-floral-printed-aline-kurta/p-mp000000031724210</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/fabindia-fuchsia-cotton-slim-fit-embellished-kurta/p-mp000000031772197</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/biba-green-printed-kurti/p-mp000000025583727</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/fabindia-multicolor-cotton-printed-short-kurta/p-mp000000031601947</t>
+    <t>2026-09-11T14:26:07.254Z</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/libas-art-womens-green-regular-fit-floral-tissue-saree-with-unstitched-blouse/p-mp000000031507672</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/tikhi-imli-orange-embellished-saree-with-unstitched-blouse/p-mp000000027316150</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/chidiyaa-sky-blue-madras-uvakai-saree/p-mp000000031065076</t>
+  </si>
+  <si>
+    <t>2026-09-11T14:26:07.255Z</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/satrani-lavender-silk-blend-woven-saree-with-unstitched-blouse/p-mp000000025698119</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/satrani-purple-silk-woven-saree-with-unstitched-blouse/p-mp000000025697895</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/satrani-red-art-silk-woven-saree-with-unstitched-blouse/p-mp000000025695941</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/kalakari-india-pink-cotton-woven-saree-with-unstitched-blouse/p-mp000000013392059</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/kalakari-india-brown-cotton-printed-saree-with-unstitched-blouse/p-mp000000013391753</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/chidiyaa-blue-cotton-graphic-saree/p-mp000000031072144</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/libas-pink-embellished-saree-with-unstitched-blouse/p-mp000000031808345</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/tikhi-imli-blue-embellished-saree-with-unstitched-blouse/p-mp000000027316405</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/silk-land-purple-silk-checked-saree-with-unstitched-blouse/p-mp000000031936844</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/tikhi-imli-green-solid-saree-with-unstitched-blouse/p-mp000000027316096</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/jaypore-turquoise-blue-linen-embellished-saree/p-mp000000027473075</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/satrani-blue-art-silk-woven-saree-with-unstitched-blouse/p-mp000000025696098</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/satrani-purple-silk-crepe-printed-saree-with-unstitched-blouse/p-mp000000025699144</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/kalakari-india-white-cotton-woven-saree-with-unstitched-blouse/p-mp000000013392085</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/kalakari-india-yellow-purple-linen-tie-dye-saree-with-unstitched-blouse/p-mp000000013391630</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/libas-art-beige-embellished-saree-with-unstitched-blouse/p-mp000000031614871</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/garden-vareli-dusty-rose-pink-embellished-saree-with-unstitched-blouse/p-mp000000031654038</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/fabindia-golden-woven-design-saree/p-mp000000031866555</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/garden-vareli-red-floral-viscose-brasso-saree/p-mp000000031912113</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/libas-brown-striped-saree-with-unstitched-blouse/p-mp000000031804842</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/jaypore-multicolour-kanjivaram-saree/p-mp000000029159150</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/jaypore-white-kota-block-printed-saree/p-mp000000029159681</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/kalakari-india-blue-cotton-printed-saree-with-unstitched-blouse/p-mp000000013391995</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/kalakari-india-white-linen-printed-saree-with-unstitched-blouse/p-mp000000013391762</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/kalakari-india-purple-cotton-printed-saree-with-unstitched-blouse/p-mp000000013391873</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/koskii-mehandi-green-embroidered-saree/p-mp000000030152612</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/koskii-onion-pink-embellished-saree/p-mp000000030152577</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/fabindia-teal-woven-design-saree/p-mp000000031866563</t>
+  </si>
+  <si>
+    <t>2026-09-11T14:26:07.256Z</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/taneira-red-silk-woven-design-saree-with-unstitched-blouse/p-mp000000031052844</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/elora-womens-yellow-floral-silk-saree-with-unstitched-blouse/p-mp000000031767216</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/kalakari-india-turquoise-cotton-woven-saree-with-unstitched-blouse/p-mp000000012849310</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/satrani-purple-silk-woven-saree-with-unstitched-blouse/p-mp000000025697863</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/kalakari-india-lime-green-printed-saree-with-unstitched-blouse/p-mp000000013391818</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/kalakari-india-beige-blue-cotton-printed-saree-with-unstitched-blouse/p-mp000000013391962</t>
+  </si>
+  <si>
+    <t>https://tatacliq.com/kalakari-india-peach-printed-saree-with-unstitched-blouse/p-mp000000013391807</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF374151"/>
+      <sz val="10"/>
+      <name val="Ui-sans-serif"/>
     </font>
     <font>
       <color rgb="FF9CA3AF"/>
@@ -201,9 +212,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -546,7 +558,7 @@
   <dimension ref="A1:E158"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
-    <col min="1" max="1" width="110.42578125" customWidth="1"/>
+    <col min="1" max="1" width="113.42578125" customWidth="1"/>
     <col min="2" max="2" width="8.140625" customWidth="1"/>
     <col min="3" max="3" width="8.28515625" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" customWidth="1"/>
@@ -570,26 +582,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
         <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -597,10 +603,10 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -608,10 +614,10 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -619,438 +625,438 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D22" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C29" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C30" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D30" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C31" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D31" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>37</v>
+      <c r="A32" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="C32" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D32" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>38</v>
+      <c r="A33" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D33" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>39</v>
+      <c r="A34" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="C34" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>40</v>
+      <c r="A35" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="C35" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D35" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" t="s">
         <v>41</v>
       </c>
-      <c r="C36" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>42</v>
+      <c r="A37" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="C37" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D37" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>43</v>
+      <c r="A38" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="C38" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D38" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>44</v>
+      <c r="A39" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="C39" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D39" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>45</v>
+      <c r="A40" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D40" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>46</v>
+      <c r="A41" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="C41" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D41" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" s="1"/>
+      <c r="A121" s="2"/>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="1"/>
+      <c r="A122" s="2"/>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" s="1"/>
+      <c r="A126" s="2"/>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" s="1"/>
+      <c r="A127" s="2"/>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" s="1"/>
+      <c r="A133" s="2"/>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" s="1"/>
+      <c r="A134" s="2"/>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="1"/>
+      <c r="A139" s="2"/>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" s="1"/>
+      <c r="A143" s="2"/>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" s="1"/>
+      <c r="A144" s="2"/>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" s="1"/>
+      <c r="A147" s="2"/>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" s="1"/>
+      <c r="A152" s="2"/>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" s="1"/>
+      <c r="A153" s="2"/>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" s="1"/>
+      <c r="A157" s="2"/>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" s="1"/>
+      <c r="A158" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/input/products.xlsx
+++ b/input/products.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="products" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="49">
   <si>
     <t>url</t>
   </si>
@@ -31,143 +31,913 @@
     <t>error</t>
   </si>
   <si>
-    <t>https://tatacliq.com/koskii-rani-pink-zari-saree/p-mp000000030180975</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/soch-womens-orange-regular-fit-bandhani-viscose-saree/p-mp000000031768720</t>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/adidas-black-printed-cotton-w-bl-t-tshirt/p-mp000000015086124</t>
+    </r>
   </si>
   <si>
     <t>done</t>
   </si>
   <si>
-    <t>2026-09-11T14:26:07.254Z</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/libas-art-womens-green-regular-fit-floral-tissue-saree-with-unstitched-blouse/p-mp000000031507672</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/tikhi-imli-orange-embellished-saree-with-unstitched-blouse/p-mp000000027316150</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/chidiyaa-sky-blue-madras-uvakai-saree/p-mp000000031065076</t>
-  </si>
-  <si>
-    <t>2026-09-11T14:26:07.255Z</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/satrani-lavender-silk-blend-woven-saree-with-unstitched-blouse/p-mp000000025698119</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/satrani-purple-silk-woven-saree-with-unstitched-blouse/p-mp000000025697895</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/satrani-red-art-silk-woven-saree-with-unstitched-blouse/p-mp000000025695941</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/kalakari-india-pink-cotton-woven-saree-with-unstitched-blouse/p-mp000000013392059</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/kalakari-india-brown-cotton-printed-saree-with-unstitched-blouse/p-mp000000013391753</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/chidiyaa-blue-cotton-graphic-saree/p-mp000000031072144</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/libas-pink-embellished-saree-with-unstitched-blouse/p-mp000000031808345</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/tikhi-imli-blue-embellished-saree-with-unstitched-blouse/p-mp000000027316405</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/silk-land-purple-silk-checked-saree-with-unstitched-blouse/p-mp000000031936844</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/tikhi-imli-green-solid-saree-with-unstitched-blouse/p-mp000000027316096</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/jaypore-turquoise-blue-linen-embellished-saree/p-mp000000027473075</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/satrani-blue-art-silk-woven-saree-with-unstitched-blouse/p-mp000000025696098</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/satrani-purple-silk-crepe-printed-saree-with-unstitched-blouse/p-mp000000025699144</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/kalakari-india-white-cotton-woven-saree-with-unstitched-blouse/p-mp000000013392085</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/kalakari-india-yellow-purple-linen-tie-dye-saree-with-unstitched-blouse/p-mp000000013391630</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/libas-art-beige-embellished-saree-with-unstitched-blouse/p-mp000000031614871</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/garden-vareli-dusty-rose-pink-embellished-saree-with-unstitched-blouse/p-mp000000031654038</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/fabindia-golden-woven-design-saree/p-mp000000031866555</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/garden-vareli-red-floral-viscose-brasso-saree/p-mp000000031912113</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/libas-brown-striped-saree-with-unstitched-blouse/p-mp000000031804842</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/jaypore-multicolour-kanjivaram-saree/p-mp000000029159150</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/jaypore-white-kota-block-printed-saree/p-mp000000029159681</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/kalakari-india-blue-cotton-printed-saree-with-unstitched-blouse/p-mp000000013391995</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/kalakari-india-white-linen-printed-saree-with-unstitched-blouse/p-mp000000013391762</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/kalakari-india-purple-cotton-printed-saree-with-unstitched-blouse/p-mp000000013391873</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/koskii-mehandi-green-embroidered-saree/p-mp000000030152612</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/koskii-onion-pink-embellished-saree/p-mp000000030152577</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/fabindia-teal-woven-design-saree/p-mp000000031866563</t>
-  </si>
-  <si>
-    <t>2026-09-11T14:26:07.256Z</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/taneira-red-silk-woven-design-saree-with-unstitched-blouse/p-mp000000031052844</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/elora-womens-yellow-floral-silk-saree-with-unstitched-blouse/p-mp000000031767216</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/kalakari-india-turquoise-cotton-woven-saree-with-unstitched-blouse/p-mp000000012849310</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/satrani-purple-silk-woven-saree-with-unstitched-blouse/p-mp000000025697863</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/kalakari-india-lime-green-printed-saree-with-unstitched-blouse/p-mp000000013391818</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/kalakari-india-beige-blue-cotton-printed-saree-with-unstitched-blouse/p-mp000000013391962</t>
-  </si>
-  <si>
-    <t>https://tatacliq.com/kalakari-india-peach-printed-saree-with-unstitched-blouse/p-mp000000013391807</t>
+    <t>2026-09-13T04:24:03.618Z</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/adidas-originals-white-printed-sports-tshirt/p-mp000000023599640</t>
+    </r>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[
+  {
+    "expected": "string",
+    "code": "invalid_type",
+    "path": [
+      "product",
+      "name"
+    ],
+    "message": "Invalid input: expected string, received null"
+  }
+]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/domyos-black-cotton-plain-sports-tshirt/p-mp000000025271213</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/jockey-aw88-women-super-combed-cotton-rich-relaxed-fit-solid-curved-hem-styled-half-sleeve-tshirt/p-mp000000031550705</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/feier-black-nylon-solid-long-sleeves-tshirt/p-mp000000027268982</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/reebok-women-tank-top/p-mp000000030659952</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/ajile-by-pantaloons-black-polyester-sports-tshirt/p-mp000000031692470</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/amante-grey-relaxed-fit-solid-tshirt/p-mp000000027691397</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/kiprun-purple-regular-fit-sports-tshirt/p-mp000000028563911</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/clovia-navy-blue-cotton-sports-tshirt/p-mp000000031438521</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/adidas-black-w-fi-3s-tshirt/p-mp000000026405849</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/adidas-originals-black-ess-crop-top/p-mp000000026405405</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/under-armour-blue-rival-core-relaxed-fit-tshirt/p-mp000000031707320</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/jockey-mw87-womens-microfiber-fabric-regular-fit-half-sleeve-breathable-mesh-tshirt/p-mp000000029926540</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/feier-pink-relaxed-fit-tank-top/p-mp000000024007011</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/silvertraq-dazzling-blue-solid-sports-t-shirt/p-mp000000031824932</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/the-souled-store-disney-princess-brave-women-oversized-jersey/p-mp000000030167565</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/cava-athleisure-cobalt-overlap-tee/p-mp000000029697025</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/van-heusen-grey-relaxed-fit-tshirt/p-mp000000027092503</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/clovia-purple-regular-fit-abstract-sports-polo-tshirt/p-mp000000032023812</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/under-armour-pink-tech-knockout-relaxed-fit-tank/p-mp000000031365970</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/athlisis-yellow-edry-tech-solid-sports-tshirt/p-mp000000028697561</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/wedze-black-plain-thermal-top/p-mp000000025268474</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/athlisis-red-edry-tech-solid-sports-tshirt/p-mp000000028697116</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/cava-athleisure-navy-overlap-tee/p-mp000000030031917</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/the-souled-store-tss-originals-silly-peppers-women-oversized-jerseys/p-mp000000031133449</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/alcis-mint-green-regular-fit-crop-top/p-mp000000030580104</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/olaian-black-plain-surfing-tshirt/p-mp000000025268311</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/domin8-dark-grey-regular-fit-printed-tank-top/p-mp000000028249404</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/soie-black-printed-sports-crop-top/p-mp000000019457249</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/domyos-beige-plain-tshirt/p-mp000000025271089</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/skechers-coral-regular-fit-printed-tshirt/p-mp000000029831158</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/skechers-blue-regular-fit-printed-tshirt/p-mp000000029831157</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/alcis-lavender-regular-fit-tshirt/p-mp000000030580015</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/amante-green-relaxed-fit-graphic-tshirt/p-mp000000027691442</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/silvertraq-java-solid-sports-t-shirt/p-mp000000031823598</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/ajile-by-pantaloons-jet-black-relaxed-fit-sports-tshirt/p-mp000000031991626</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/van-heusen-purple-relaxed-fit-tshirt/p-mp000000027092506</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/kalenji-pink-plain-tshirt/p-mp000000025270164</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>tatacliq.com</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
+        <scheme val="minor"/>
+        <sz val="10"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>/enamor-relaxed-tee-relaxed-fit-round-neckline-a316/p-mp000000030893460</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -176,28 +946,18 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF374151"/>
-      <sz val="10"/>
-      <name val="Ui-sans-serif"/>
-    </font>
-    <font>
-      <color rgb="FF9CA3AF"/>
+      <u/>
+      <color rgb="FF0000FF"/>
       <sz val="10"/>
       <name val="Ui-sans-serif"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -212,10 +972,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -244,44 +1003,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -309,14 +1068,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -344,6 +1120,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -355,180 +1148,136 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
+            <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
     <a:lnDef>
       <a:spPr/>
       <a:bodyPr/>
@@ -550,20 +1299,18 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E158"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
-  <cols>
-    <col min="1" max="1" width="113.42578125" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" customWidth="1"/>
-    <col min="5" max="5" width="5.42578125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -582,361 +1329,370 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>6</v>
+      <c r="A3" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
+      <c r="A4" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>10</v>
+      <c r="A5" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>11</v>
+      <c r="A6" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>13</v>
+      <c r="A7" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>14</v>
+      <c r="A8" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>15</v>
+      <c r="A9" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>16</v>
+      <c r="A10" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>17</v>
+      <c r="A11" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>18</v>
+      <c r="A12" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>19</v>
+      <c r="A13" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>20</v>
+      <c r="A14" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>21</v>
+      <c r="A15" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>22</v>
+      <c r="A16" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>23</v>
+      <c r="A17" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>24</v>
+      <c r="A18" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>25</v>
+      <c r="A19" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>26</v>
+      <c r="A20" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>27</v>
+      <c r="A21" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D21" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>28</v>
+      <c r="A22" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>29</v>
+      <c r="A23" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>30</v>
+      <c r="A24" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>31</v>
+      <c r="A25" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>32</v>
+      <c r="A26" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="C26" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>33</v>
+      <c r="A27" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="C27" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>34</v>
+      <c r="A28" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="C28" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D28" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>35</v>
+      <c r="A29" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D29" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>36</v>
+      <c r="A30" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="C30" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D30" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>37</v>
+      <c r="A31" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="C31" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D31" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D32" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D33" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>40</v>
+      <c r="A34" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="C34" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D34" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -944,10 +1700,10 @@
         <v>42</v>
       </c>
       <c r="C35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -955,10 +1711,10 @@
         <v>43</v>
       </c>
       <c r="C36" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D36" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -966,10 +1722,10 @@
         <v>44</v>
       </c>
       <c r="C37" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D37" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -977,10 +1733,10 @@
         <v>45</v>
       </c>
       <c r="C38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D38" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -988,10 +1744,10 @@
         <v>46</v>
       </c>
       <c r="C39" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D39" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -999,10 +1755,10 @@
         <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D40" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1010,56 +1766,55 @@
         <v>48</v>
       </c>
       <c r="C41" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D41" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" s="2"/>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="2"/>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" s="2"/>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" s="2"/>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" s="2"/>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" s="2"/>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="2"/>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" s="2"/>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" s="2"/>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" s="2"/>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" s="2"/>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" s="2"/>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" s="2"/>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" s="2"/>
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="A3" r:id="rId2"/>
+    <hyperlink ref="A4" r:id="rId3"/>
+    <hyperlink ref="A5" r:id="rId4"/>
+    <hyperlink ref="A6" r:id="rId5"/>
+    <hyperlink ref="A7" r:id="rId6"/>
+    <hyperlink ref="A8" r:id="rId7"/>
+    <hyperlink ref="A9" r:id="rId8"/>
+    <hyperlink ref="A10" r:id="rId9"/>
+    <hyperlink ref="A11" r:id="rId10"/>
+    <hyperlink ref="A12" r:id="rId11"/>
+    <hyperlink ref="A13" r:id="rId12"/>
+    <hyperlink ref="A14" r:id="rId13"/>
+    <hyperlink ref="A15" r:id="rId14"/>
+    <hyperlink ref="A16" r:id="rId15"/>
+    <hyperlink ref="A17" r:id="rId16"/>
+    <hyperlink ref="A18" r:id="rId17"/>
+    <hyperlink ref="A19" r:id="rId18"/>
+    <hyperlink ref="A20" r:id="rId19"/>
+    <hyperlink ref="A21" r:id="rId20"/>
+    <hyperlink ref="A22" r:id="rId21"/>
+    <hyperlink ref="A23" r:id="rId22"/>
+    <hyperlink ref="A24" r:id="rId23"/>
+    <hyperlink ref="A25" r:id="rId24"/>
+    <hyperlink ref="A26" r:id="rId25"/>
+    <hyperlink ref="A27" r:id="rId26"/>
+    <hyperlink ref="A28" r:id="rId27"/>
+    <hyperlink ref="A29" r:id="rId28"/>
+    <hyperlink ref="A30" r:id="rId29"/>
+    <hyperlink ref="A31" r:id="rId30"/>
+    <hyperlink ref="A32" r:id="rId31"/>
+    <hyperlink ref="A33" r:id="rId32"/>
+    <hyperlink ref="A34" r:id="rId33"/>
+    <hyperlink ref="A35" r:id="rId34"/>
+    <hyperlink ref="A36" r:id="rId35"/>
+    <hyperlink ref="A37" r:id="rId36"/>
+    <hyperlink ref="A38" r:id="rId37"/>
+    <hyperlink ref="A39" r:id="rId38"/>
+    <hyperlink ref="A40" r:id="rId39"/>
+    <hyperlink ref="A41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/input/products.xlsx
+++ b/input/products.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="329">
   <si>
     <t>url</t>
   </si>
@@ -28,7 +28,7 @@
     <t>error</t>
   </si>
   <si>
-    <t>https://agarolifestyle.com/products/regency-multi-cook-kettle-with-steamer-1-2-litres-sea-green</t>
+    <t>https://www.nykaa.com/bronson-professional-3d-body-massager-y-shape-for-skin-skin-lifting-and-slimming/p/677038?productId=677038&amp;pps=1</t>
   </si>
   <si>
     <t/>
@@ -37,16 +37,967 @@
     <t>done</t>
   </si>
   <si>
-    <t>2026-09-15T10:47:45.681Z</t>
-  </si>
-  <si>
-    <t>https://agarolifestyle.com/products/agaro-supreme-plus-high-pressure-washer-2200-watts-7-5l-min-flow-rate-140-bars-8-meters-outlet-hose-5-mtr-power-cord-for-car-bike-and-home-cleaning-purpose-yellow</t>
-  </si>
-  <si>
-    <t>https://agarolifestyle.com/products/marvel-tyre-inflator-for-cars-12v-upto-150-psi-120-w-powerful-motor-up-to-3m-long-cable-digital-display-multiple-nozzles</t>
-  </si>
-  <si>
-    <t>https://agarolifestyle.com/products/agaro-royal-electric-spin-scrubber-cleaning-brush-scrubber-for-home-400rpm-mins-8-replaceable-brush-heads-90mins-work-time-3-adjustable-size-2-adjustable-speeds-for-bathroom-shower-bathtub-glass-car</t>
+    <t>2026-09-15T17:41:50.890Z</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/bronson-professional-jade-roller-massager-tool-green/p/430198?productId=430198&amp;pps=2</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/le-marbelle-ice-roller-for-face-neck-eye-purple/p/8125908?productId=8125908&amp;pps=3</t>
+  </si>
+  <si>
+    <t>2026-09-15T17:41:50.891Z</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/bronson-professional-classic-mini-silicone-ice-facial-roller/p/10227335?productId=10227335&amp;pps=4</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/bronson-professional-oil-absorbing-volcanic-face-roller/p/10483349?productId=10483349&amp;pps=5</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/be-bodywise-scalp-massager-helps-exfoliate-and-stimulates-scalp/p/5029278?productId=5029278&amp;pps=6</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/agaro-3-in-1-electric-rose-quartz-face-roller-anti-aging-facial-massager-rose-gold/p/4251252?productId=4251252&amp;pps=7</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/matra-electric-scalp-massager-for-hair-growth-head-body/p/23595065?productId=23595065&amp;pps=8</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/mschief-electro-egg-massager-with-remote-purple/p/12423914?productId=12423914&amp;pps=9</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/le-marbelle-green-jade-gua-sha-stone-massage-tool/p/677934?productId=677934&amp;pps=10</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/vandelay-mini-mate-massager-wireless-waterproof-personal-body-massager-pink/p/5167149?productId=5167149&amp;pps=11</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/saturn-by-ghc-jade-roller-gua-sha-massage-kit/p/10932874?productId=10932874&amp;pps=12</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/tangle-teezer-scalp-exfoliator-massager-lilac/p/1155752?productId=1155752&amp;pps=13</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/kazarmaa-jade-roller-with-gua-sha-set-face-massager/p/4784222?productId=4784222&amp;pps=14</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/protouch-glow-pro-4-in-1-micro-current-toning-facial-device-grey/p/27129585?productId=27129585&amp;pps=15</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/caresmith-revive-electric-handheld-head-massager-massager-green/p/7298649?productId=7298649&amp;pps=16</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/tangle-teezer-scalp-exfoliator-massager-black/p/1155753?productId=1155753&amp;pps=17</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-ice-globes-facial-massager/p/4146679?productId=4146679&amp;pps=18</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/kazarmaa-2-in-1-manual-facial-cleansing-brush/p/19872755?productId=19872755&amp;pps=19</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/house-of-beauty-24k-face-massager-for-puffiness-reduction/p/5905184?productId=5905184&amp;pps=20</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/majestique-head-and-scalp-massager/p/6713442?productId=6713442&amp;pps=1</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/winston-rechargeable-battery-operated-3-color-led-light-therapy-face-mask/p/2754652?productId=2754652&amp;pps=2</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/signaxo-advanced-neck-face-skin-lifting-tool-device/p/17395641?productId=17395641&amp;pps=3</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/kayanara-full-body-gun-massager-for-pain-relief-with-4-attachments/p/18806291?productId=18806291&amp;pps=4</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/beardo-black-hair-scalp-massager-brush-with-soft-silicone-bristles/p/14601513?productId=14601513&amp;pps=5</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-t-shape-electric-sign-face-massage-tools/p/15168539?productId=15168539&amp;pps=6</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/agaro-cm2407-facial-cleansing-massager/p/18506249?productId=18506249&amp;pps=7</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/matra-kansa-wand-massager-for-face-body-feet/p/24506905?productId=24506905&amp;pps=8</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/gubb-oil-absorbing-face-roller/p/25601614?productId=25601614&amp;pps=9</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-black-obsidian-gua-sha-stone-for-face-neak-and-under-eye/p/4146672?productId=4146672&amp;pps=10</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/caresmith-revive-scalp-massager-with-detachable-heads-black/p/26614617?productId=26614617&amp;pps=11</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/matra-kansa-vatki-foot-massager-ayurvedic-bronze-bowl-wand-cup-for-detox/p/27260251?productId=27260251&amp;pps=12</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/agaro-3-in-1-electric-rose-quartz-face-roller-with-gua-sha/p/10633715?productId=10633715&amp;pps=13</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/protouch-led-hair-growth-therapy-comb/p/3908556?productId=3908556&amp;pps=14</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/pee-safe-domina-handheld-full-body-massager/p/2759845?productId=2759845&amp;pps=15</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/avon-new-rolling-facial-massager/p/26816691?productId=26816691&amp;pps=16</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/gorgio-professional-5-in-1-compact-face-massager-color-may-vary-gcf005/p/640791?productId=640791&amp;pps=17</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/venihea-tarangini-full-body-personal-massager-for-stress-relief/p/18306774?productId=18306774&amp;pps=18</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/le-marbelle-jade-roller-face-massager/p/677926?productId=677926&amp;pps=19</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/scalppie-intense-hair-scalp-massager-and-shampoo-brush-cotton-candy-pink/p/6157440?productId=6157440&amp;pps=20</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/le-marbelle-ice-roller-for-face-neck-eye-pink/p/8125910?productId=8125910&amp;pps=1</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/le-marbelle-ice-roller-for-face-neck-eye-black/p/8125909?productId=8125909&amp;pps=2</t>
+  </si>
+  <si>
+    <t>2026-09-15T17:41:50.892Z</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/le-marbelle-rose-quartz-gua-sha-stone-massage-tool/p/677935?productId=677935&amp;pps=3</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/le-marbelle-ice-roller-for-face-neck-eye-green/p/8125912?productId=8125912&amp;pps=4</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/gubb-sculpting-face-massager/p/7326608?productId=7326608&amp;pps=5</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-green-jade-gua-sha-stone-for-face-neck-and-under-eye/p/4146671?productId=4146671&amp;pps=6</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/skince-hot-and-cold-facial-wand-for-skin-tightening/p/26722810?productId=26722810&amp;pps=7</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/caresmith-bloom-solid-metal-face-roller-rose-gold/p/5224296?productId=5224296&amp;pps=8</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/gorgio-professional-titanium-coated-face-and-body-roller-brush-for-blood-circulation/p/492077?productId=492077&amp;pps=9</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/agaro-relaxo-h-and-massager-28w-black/p/758181?productId=758181&amp;pps=10</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/kloy-face-ice-roller/p/13287961?productId=13287961&amp;pps=11</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/caresmith-revive-scalp-massager-with-detachable-heads-blue/p/26614616?productId=26614616&amp;pps=12</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/caresmith-revive-cushion-back-massager-for-pain-relief/p/21005633?productId=21005633&amp;pps=13</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/protouch-skin-lift-combo-skin-lift-device-recovery-drops-anti-ageing-bright-firm-younger-skin/p/10241640?productId=10241640&amp;pps=14</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/furr-rechargeable-callus-remover-for-feet/p/17285177?productId=17285177&amp;pps=15</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/le-marbelle-rose-quartz-roller-and-gua-sha-massager-for-face-neck-dark-circles-and-under-eye-combo/p/6763766?productId=6763766&amp;pps=16</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/numour-g-o-a-t-smart-gua-sha/p/18875733?productId=18875733&amp;pps=17</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/healthsense-magic-vibe-cherry-body-massager-hm260/p/848408?productId=848408&amp;pps=18</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/matra-ice-globes-facial-massager-roller-tool-for-anti-aging-face-lifting-set-of-2/p/5237329?productId=5237329&amp;pps=19</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-facial-roller-and-massager/p/4146667?productId=4146667&amp;pps=20</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/plix-gua-sha-stone/p/12405309?productId=12405309&amp;pps=1</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/le-marbelle-black-obsidian-gua-sha-facial-tool/p/861333?productId=861333&amp;pps=2</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/venihea-toofanii-personal-full-body-massager/p/18306772?productId=18306772&amp;pps=3</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/kazarmaa-jade-roller-face-massager/p/4784221?productId=4784221&amp;pps=4</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/scalppie-hair-scalp-oil-applicator-black/p/19011000?productId=19011000&amp;pps=5</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/vandelay-electric-handheld-full-body-massager-rechargeable-massage-machine-for-home-white/p/5167142?productId=5167142&amp;pps=6</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-electric-head-and-body-massager-scalp-massager/p/26265792?productId=26265792&amp;pps=7</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/vandelay-magic-mate-rechargeable-personal-body-massager-for-women-men-waterproof-millenial-pink/p/5167143?productId=5167143&amp;pps=8</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/le-marbelle-ice-roller-for-face-neck-eye-blue/p/8125911?productId=8125911&amp;pps=9</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-purple-ice-roller-jade-gua-sha-faical-massage-tool/p/15168529?productId=15168529&amp;pps=10</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/caresmith-bloom-rechargeable-callus-remover/p/7298652?productId=7298652&amp;pps=11</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/pee-safe-domina-discover-personal-massager-for-women/p/16426498?productId=16426498&amp;pps=12</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-green-jade-facial-roller-and-gua-sha-for-face-neck-dark-circles-and-under-eye-treatment/p/4146669?productId=4146669&amp;pps=13</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/ikonic-me-zen-electric-scalp-massager-pearl-white-chrome/p/22265847?productId=22265847&amp;pps=14</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-gua-sha-stone-for-face-neck-and-under-eye/p/4146670?productId=4146670&amp;pps=15</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/matra-3d-roller-face-body-massager-y-shape-sculptor-for-skin-lifting-tightening/p/7668839?productId=7668839&amp;pps=16</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/agaro-royal-deep-tissue-body-massager-with-4-heads-for-full-body-relief/p/26324924?productId=26324924&amp;pps=17</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-head-scalp-massager/p/5537292?productId=5537292&amp;pps=18</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/waldon-electric-handheld-full-body-massager-with-4-massage-heads-white/p/25060554?productId=25060554&amp;pps=19</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/fyoli-neem-wooden-gua-sha-face-massager/p/12403561?productId=12403561&amp;pps=20</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/agaro-atom-plus-full-body-massager-blue/p/21732882?productId=21732882&amp;pps=1</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-gua-sha-massage-tool-rabbit-ear-shape/p/6068290?productId=6068290&amp;pps=2</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/alan-truman-scalp-days-scalp-care-therapy-brush/p/19998850?productId=19998850&amp;pps=3</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/semino-advanced-4-in-1-rechargeable-electric-facial-cleanser-and-massager-brush/p/14018930?productId=14018930&amp;pps=4</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/house-of-beauty-hob-derma-roller-0-75mm/p/411607?productId=411607&amp;pps=5</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/majestique-face-massager-ice-roller/p/3798037?productId=3798037&amp;pps=6</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-sodalite-wand-gua-sha-tool/p/5537288?productId=5537288&amp;pps=7</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/house-of-beauty-hob-jade-eye-mask-180gm/p/400805?productId=400805&amp;pps=8</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/waldon-by-dr-odin-personal-handheld-wand-massager-black/p/4297925?productId=4297925&amp;pps=9</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/majestique-jade-face-roller-massager/p/3798036?productId=3798036&amp;pps=10</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-ice-facial-roller-for-face-and-eye-silicone-ice-mold-for-facial-skin-care-tool-for-women/p/7144600?productId=7144600&amp;pps=11</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/vandelay-deep-tissue-gun-massager-electric-handheld-massager-for-pain-relief-with-wire/p/5167159?productId=5167159&amp;pps=12</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/ras-luxury-oils-jade-scalp-massager/p/23052529?productId=23052529&amp;pps=13</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-ice-facial-roller-for-face-and-eye-silicone-ice-mold-for-facial-skin-care-tool-for-women/p/7144601?productId=7144601&amp;pps=14</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-black-obsidian-gua-sha-facial-massage-tool-with-teeth-shape-sides-and-ridges/p/6068288?productId=6068288&amp;pps=15</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/signaxo-facial-ice-globes-assorted-color-pink-blue/p/13385481?productId=13385481&amp;pps=16</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/rhe-cosmetics-3d-facefit-flex-y-shape-roller-massager/p/16654771?productId=16654771&amp;pps=17</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-jade-bottle-roller-for-face-eye-neck/p/5537286?productId=5537286&amp;pps=18</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/matra-ice-globes-facial-massager-roller-tool-for-anti-aging-face-lifting/p/5237324?productId=5237324&amp;pps=19</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-black-obsidian-face-roller-and-rabbit-ear-shape-gua-sha-massage-tool-set/p/6068329?productId=6068329&amp;pps=20</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/allure-gua-sha-stone-rose-quartz/p/4477269?productId=4477269&amp;pps=1</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/house-of-beauty-led-3-in-1-scalp-massager-with-red-blue-light-therapy/p/19367239?productId=19367239&amp;pps=2</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/kazarmaa-wooden-handheld-body-calf-massager-acupressure-roller/p/5885104?productId=5885104&amp;pps=3</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-hot-massage-stones-16-pcs-electric-hot-stones-massage-set-with-warmer/p/6068331?productId=6068331&amp;pps=4</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-ice-facial-roller-for-face-and-eye-for-women/p/9041625?productId=9041625&amp;pps=5</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-pink-ice-roller-rose-quartz-gua-sha-faical-massage-tool/p/15168535?productId=15168535&amp;pps=6</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/gubb-facial-ice-wave-ball-for-face-and-eyes-facial-cooling-massager-pack-of-2/p/6801980?productId=6801980&amp;pps=7</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/protouch-glow-pro-4-in-1-micro-current-toning-facial-device-pink/p/27129586?productId=27129586&amp;pps=8</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-wand-gua-sha-tool/p/4146702?productId=4146702&amp;pps=9</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/house-of-beauty-3d-face-massager-for-face-contouring/p/5905185?productId=5905185&amp;pps=10</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/milagro-beauty-volcanic-roller/p/4945787?productId=4945787&amp;pps=11</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/le-marbelle-rose-quartz-facial-massage-roller/p/677927?productId=677927&amp;pps=12</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/mschief-adagio-intimate-sensual-massager-peach/p/12423917?productId=12423917&amp;pps=13</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/gorgio-professional-scalp-massager-for-handheld-head-massage-tingle/p/13773783?productId=13773783&amp;pps=14</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/le-marbelle-jade-roller-and-gua-sha-massager-for-face-neck-dark-circles-and-under-eye-combo/p/6763765?productId=6763765&amp;pps=15</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/house-of-beauty-hob-body-cups-60gm/p/400807?productId=400807&amp;pps=16</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/plix-jade-roller/p/12405308?productId=12405308&amp;pps=17</t>
+  </si>
+  <si>
+    <t>2026-09-15T17:41:50.893Z</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/plix-face-ice-roller/p/12405311?productId=12405311&amp;pps=18</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-jade-face-roller-and-jade-gua-sha-with-teeth-shape-sides-and-ridges-massage-tool-set/p/6068325?productId=6068325&amp;pps=19</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-roller-bottle-for-face-neck-eye/p/5537287?productId=5537287&amp;pps=20</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/ras-luxury-oils-rose-quartz-gua-sha/p/4747701?productId=4747701&amp;pps=1</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/ras-luxury-oils-jade-gua-sha/p/1080687?productId=1080687&amp;pps=2</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/kazarmaa-wooden-roller-with-spikes-for-body-stress-acupressure-pain-relief-massager-brown/p/5885105?productId=5885105&amp;pps=3</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/gubb-ice-roller-for-face-eyes-neck/p/10875154?productId=10875154&amp;pps=4</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/kayanara-original-rose-quartz-stone-gua-sha/p/18097711?productId=18097711&amp;pps=5</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/kayanara-handheld-deep-scalp-kneading-massager-for-hair-growth-relaxation/p/18806292?productId=18806292&amp;pps=6</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/house-of-beauty-face-lift-pro-micro-massager/p/14064485?productId=14064485&amp;pps=7</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/yourhappylife-dermateq-silver-coated-vibrating-face-massager/p/12754162?productId=12754162&amp;pps=8</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/gubb-jade-mushroom-stone-face-massager/p/7325863?productId=7325863&amp;pps=9</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/gorgio-professional-hot-and-cool-skin-care-device-ds-v08/p/7925843?productId=7925843&amp;pps=10</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/house-of-beauty-kansa-wand-for-face-body-2-pieces/p/2739004?productId=2739004&amp;pps=11</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/natural-vibes-light-green-jade-roller-massager-with-free-gold-beauty-elixir-oil-for-face/p/1276892?productId=1276892&amp;pps=12</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-white-opalite-gua-sha-tool/p/4146689?productId=4146689&amp;pps=13</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-gua-sha-leaf-shape-gua-sha-and-rabbit-ear-shape-gua-sha-massage-tool-set/p/6068314?productId=6068314&amp;pps=14</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-and-jade-mushroom-gua-sha-set/p/4146684?productId=4146684&amp;pps=15</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/lifelong-llm18-air-pressure-massager-brown/p/809560?productId=809560&amp;pps=16</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/fyoli-rose-quartz-vibrating-facial-roller-and-undereye-massager/p/4906329?productId=4906329&amp;pps=17</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/scalppie-intense-hair-scalp-massager-and-shampoo-brush-teal-green/p/6157442?productId=6157442&amp;pps=18</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/scalppie-intense-hair-scalp-massager-and-shampoo-brush-rose-pink/p/6157438?productId=6157438&amp;pps=19</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/house-of-beauty-magic-wand-high-frequency-5-pcs/p/2739003?productId=2739003&amp;pps=20</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/signaxo-rose-quartz-pink-jade-roller-with-guasha-set/p/5205873?productId=5205873&amp;pps=1</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-black-obsidian-roller-and-gua-sha-set/p/4146678?productId=4146678&amp;pps=2</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/scalppie-intense-hair-scalp-massager-and-shampoo-brush-charcoal-black/p/6157446?productId=6157446&amp;pps=3</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-roller-gua-sha-face-massager-with-pink-ice-roller/p/15168538?productId=15168538&amp;pps=4</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-roller-and-gua-sha-for-face-neck-dark-circles-and-under-eye-treatment/p/4146666?productId=4146666&amp;pps=5</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/gorgio-professional-rose-quartz-heart-shape-gausha-grq035/p/640788?productId=640788&amp;pps=6</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-jade-roller-gua-sha-face-massager-with-pink-ice-roller/p/15168537?productId=15168537&amp;pps=7</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/semino-advanced-deep-cleansing-sonic-facial-silicone-rechargeable-massager-brush-blue/p/14018931?productId=14018931&amp;pps=8</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/semino-advanced-led-light-therapy-face-mask-white/p/12408933?productId=12408933&amp;pps=9</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/house-of-beauty-hob-derma-roller-1-00mm/p/411608?productId=411608&amp;pps=10</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-face-roller-and-gua-sha-set-with-rose-quartz-mushroom-gua-sha/p/4146699?productId=4146699&amp;pps=11</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/gubb-usa-3d-face-body-massager-for-skin-lifting-tightening-relaxation/p/3845975?productId=3845975&amp;pps=12</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/signaxo-himalyan-green-jade-roller-with-guasha-set/p/5205872?productId=5205872&amp;pps=13</t>
+  </si>
+  <si>
+    <t>2026-09-15T17:41:50.894Z</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/fyoli-ice-globe-facial-roller-massager-for-depuffing-skin-tightening-and-anti-aging/p/8779765?productId=8779765&amp;pps=14</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/ras-luxury-oils-jade-facial-roller-1pc/p/637572?productId=637572&amp;pps=15</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-green-jade-spoon-shape-gua-sha-massage-tool/p/6068303?productId=6068303&amp;pps=16</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/makeup-by-siti-3d-facefit-flex-y-shape-roller-massager/p/16654772?productId=16654772&amp;pps=17</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/majestique-2-pcs-gua-sha-facial-tools-natural-guasha-tool-for-face/p/8324513?productId=8324513&amp;pps=18</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/vandelay-deep-tissue-gun-massager-electric-handheld-massager-for-pain-relief-wireless/p/5167158?productId=5167158&amp;pps=19</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-mushroom-gus-sha-tool/p/4146680?productId=4146680&amp;pps=20</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-black-obsidian-leaf-shape-gua-sha-facial-massage-tool-with-teeth-shape-edges/p/6068285?productId=6068285&amp;pps=1</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/mymuse-mini-lavender-haze-personal-massager-for-women/p/12710290?productId=12710290&amp;pps=2</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-jade-mushroom-gua-sha-tool/p/4146681?productId=4146681&amp;pps=3</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/vandelay-silicon-electronic-double-sided-vibrating-back-massager-with-thick-silicon-bristles-pink/p/7364015?productId=7364015&amp;pps=4</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-pink-ice-roller-black-obsidian-gua-sha-faical-massage-tool/p/15168536?productId=15168536&amp;pps=5</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/kazarmaa-3d-roller-face-body-massager/p/6993380?productId=6993380&amp;pps=6</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-sodalite-mushroom-rabbit-ear-and-teeth-edge-gua-sha-massage-tool-set/p/6068320?productId=6068320&amp;pps=7</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-black-obsidian-comb-edge-gua-sha-facial-massage-tool/p/6068301?productId=6068301&amp;pps=8</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/house-of-beauty-collagen-face-roller/p/930214?productId=930214&amp;pps=9</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/semino-black-obsidian-face-roller-with-gua-sha-stone/p/18622898?productId=18622898&amp;pps=10</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/gubb-usa-rose-quartz-face-roller-face-massager-for-wrinkles-fine-lines-skin-firming/p/3846005?productId=3846005&amp;pps=11</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-sodalite-gua-sha-facial-massage-tool-with-teeth-shape-sides-and-ridges/p/6068289?productId=6068289&amp;pps=12</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-purple-ice-roller-rose-quartz-gua-sha-faical-massage-tool/p/15168530?productId=15168530&amp;pps=13</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-white-opalite-face-roller-and-gua-sha-set/p/4146690?productId=4146690&amp;pps=14</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/house-of-beauty-quartz-guasha/p/5905183?productId=5905183&amp;pps=15</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/house-of-beauty-hob-derma-roller-0-25mm/p/411606?productId=411606&amp;pps=16</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/kayanara-original-rose-quartz-stone-face-roller-gua-sha-massager-set/p/18097713?productId=18097713&amp;pps=17</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/house-of-beauty-jade-guasha/p/5905182?productId=5905182&amp;pps=18</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-pink-ice-roller-jade-gua-sha-faical-massage-tool/p/15168534?productId=15168534&amp;pps=19</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/house-of-beauty-hob-paraffin-socks-for-feet-180gm/p/400809?productId=400809&amp;pps=20</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/healthsense-toner-pro-handheld-body-massager-hm210/p/848407?productId=848407&amp;pps=1</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-gua-sha-and-mushroom-gua-sha-facial-massage-tool/p/6068305?productId=6068305&amp;pps=2</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/house-of-beauty-led-5-in-1-scalp-massager-with-vibrations-red-blue-light/p/19367238?productId=19367238&amp;pps=3</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/kazarmaa-ice-roller-massage-for-face-toning-green/p/7774525?productId=7774525&amp;pps=4</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/vega-rose-quartz-jade-roller-fr-01/p/1427667?productId=1427667&amp;pps=5</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-jade-gua-sha-and-mushroom-gua-sha-facial-massage-tool/p/6068306?productId=6068306&amp;pps=6</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/semino-pure-jade-green-adventurine-roller-for-face/p/12408939?productId=12408939&amp;pps=7</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/kazarmaa-ice-roller-massage-for-face-toning-pink/p/7774524?productId=7774524&amp;pps=8</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/house-of-beauty-healty-skin-blue-ice-roller/p/515439?productId=515439&amp;pps=9</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-wing-shaped-gua-sha-facial-tool/p/4146693?productId=4146693&amp;pps=10</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/house-of-beauty-hob-derma-roller-9gm/p/400801?productId=400801&amp;pps=11</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/kayanara-original-rose-quartz-stone-face-roller/p/18097712?productId=18097712&amp;pps=12</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/natural-vibes-activated-shower-gel-body-wash/p/13507821?productId=13507821&amp;pps=13</t>
+  </si>
+  <si>
+    <t>2026-09-15T17:41:50.895Z</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/natural-vibes-white-crystal-quartz-roller-massager/p/1226318?productId=1226318&amp;pps=14</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/foreo-ufo-mini-2-pearl-pink/p/5094072?productId=5094072&amp;pps=15</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/house-of-beauty-hob-derma-roller-0-25mm/p/411605?productId=411605&amp;pps=16</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/nykaa-face-massage-rollers/p/953231?productId=953231&amp;pps=17</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/be-bodywise-complete-hair-fall-control-kit-massager-ahs-conditioner-3-piece/p/7949246?productId=7949246&amp;pps=18</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/purearth-kwansha-facial-beauty-coin/p/583657?productId=583657&amp;pps=19</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/the-rolling-concept-jade-gua-sha-stone-1pc/p/664468?productId=664468&amp;pps=20</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/kazarmaa-ice-roller-massage-for-face-toning-blue/p/8523628?productId=8523628&amp;pps=1</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/riyo-herbs-rose-quartz-face-roller-massager/p/5065834?productId=5065834&amp;pps=2</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-jade-comb-edge-gua-sha-facial-massage-tool/p/6068299?productId=6068299&amp;pps=3</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-white-mushroom-gua-sha-tool/p/4146683?productId=4146683&amp;pps=4</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-butterfly-gua-sha-facial-massage-tool/p/5537285?productId=5537285&amp;pps=5</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/vandelay-silicon-electronic-double-sided-vibrating-back-massager-with-thick-silicon-bristles-green/p/7364016?productId=7364016&amp;pps=6</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-leaf-shape-gua-sha-facial-massage-tool-with-teeth-shape-edges/p/6068283?productId=6068283&amp;pps=7</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/waldon-by-dr-odin-electric-vibrating-foam-yoga-roller-1/p/4298218?productId=4298218&amp;pps=8</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-roller-gua-sha-face-massager-with-purple-ice-roller/p/15168533?productId=15168533&amp;pps=9</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/semino-3-in-1-himalayan-face-jade-rollers-with-guasha-stone/p/18622900?productId=18622900&amp;pps=10</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-teeth-shape-gua-sha-tool/p/4146691?productId=4146691&amp;pps=11</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/epique-switzerland-sonic-cleansing-pod/p/583212?productId=583212&amp;pps=12</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/kazarmaa-black-jade-roller-face-massager/p/19872754?productId=19872754&amp;pps=13</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/signaxo-himalyan-green-jade-roller/p/5586289?productId=5586289&amp;pps=14</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-green-jade-roller-and-rose-quartz-gua-sha-facial-massage-tool-set/p/5537290?productId=5537290&amp;pps=15</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-green-jade-leaf-shape-gua-sha-facial-massage-tool-with-teeth-shape-edges/p/6068284?productId=6068284&amp;pps=16</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/healthsense-enhance-electric-facial-roller-massager-with-roller-head/p/2783503?productId=2783503&amp;pps=17</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/semino-natural-white-face-jade-roller-with-gua-sha-stone/p/18622899?productId=18622899&amp;pps=18</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-green-jade-facial-roller-and-massager/p/4146668?productId=4146668&amp;pps=19</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/bungalow-beauty-green-jade-gua-sha-facial-massage-tool/p/19939785?productId=19939785&amp;pps=20</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/kazarmaa-ice-roller-massage-for-face-toning-purple/p/9718466?productId=9718466&amp;pps=1</t>
+  </si>
+  <si>
+    <t>2026-09-15T17:41:50.896Z</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/the-rolling-concept-rose-quartz-facial-roller-1pc/p/664467?productId=664467&amp;pps=2</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-spoon-shape-gua-sha-facial-tool/p/4146695?productId=4146695&amp;pps=3</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-ice-facial-roller-for-face-and-eye-silicone-ice-mold-for-facial-skin-care-tool-for-women/p/7144599?productId=7144599&amp;pps=4</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-roller-and-wing-shaped-gua-sha-with-rose-quartz-mushroom-gua-sha/p/4146700?productId=4146700&amp;pps=5</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-gua-sha-facial-massage-tool-with-teeth-shape-sides-and-ridges/p/6068286?productId=6068286&amp;pps=6</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-handmade-natural-sodalite-mushroom-gua-sha-scraping-massage-tool/p/6068294?productId=6068294&amp;pps=7</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-face-roller-and-leaf-shape-gua-sha-massage-tool-set/p/6068321?productId=6068321&amp;pps=8</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-wing-shape-gua-sha-and-wand-gua-sha-set/p/5537289?productId=5537289&amp;pps=9</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/leaf-monk-rose-quartz-gua-sha-face-massage-tool/p/14739298?productId=14739298&amp;pps=10</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/scalppie-intense-hair-scalp-massager-and-shampoo-brush-orchid-purple/p/6157444?productId=6157444&amp;pps=11</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-face-roller-and-mushroom-gua-sha-facial-massage-tool-set/p/6068308?productId=6068308&amp;pps=12</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-face-roller-and-wing-shaped-gua-sha-facial-tool/p/4146694?productId=4146694&amp;pps=13</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-jade-roller-for-face-massager-and-wing-shape-gua-sha-facial-massage-tool-set/p/6068296?productId=6068296&amp;pps=14</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-green-jade-gua-sha-massage-tool-rabbit-ear-shape/p/6068291?productId=6068291&amp;pps=15</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-black-obsidian-face-roller-and-leaf-shape-gua-sha-massage-tool-set/p/6068327?productId=6068327&amp;pps=16</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-gua-sha-wing-shape-gua-sha-and-rabbit-ear-shape-gua-sha-massage-tool-set/p/6068312?productId=6068312&amp;pps=17</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-green-jade-gua-sha-facial-massage-tool-with-teeth-shape-sides-and-ridges/p/6068287?productId=6068287&amp;pps=18</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/waldon-by-dr-odin-electric-vibrating-foam-yoga-roller/p/4298219?productId=4298219&amp;pps=19</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/mymuse-pulse-personal-massager-morning-light/p/8802574?productId=8802574&amp;pps=20</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-black-obsidian-gua-sha-and-mushroom-gua-sha-facial-massage-tool/p/6068307?productId=6068307&amp;pps=1</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-jade-roller-gua-sha-face-massager-with-purple-ice-roller/p/15168532?productId=15168532&amp;pps=2</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-roller-and-gua-sha-with-wing-shape-gua-sha-set/p/5537291?productId=5537291&amp;pps=3</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-black-obsidian-gua-sha-massage-tool-rabbit-ear-shape/p/6068292?productId=6068292&amp;pps=4</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/house-of-beauty-hob-jade-roller-70gm/p/400803?productId=400803&amp;pps=5</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-purple-ice-roller-black-obsidian-gua-sha-faical-massage-tool/p/15168531?productId=15168531&amp;pps=6</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-jade-roller-and-comb-edge-gua-sha-massage-tool-set/p/6068300?productId=6068300&amp;pps=7</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-green-jade-aventurine-face-roller-and/p/4146701?productId=4146701&amp;pps=8</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/zoe-ayla-rose-quartz-luxurious-facial-roller-noiseless/p/5679080?productId=5679080&amp;pps=9</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-butterfly-gua-sha-facial-tool/p/4146696?productId=4146696&amp;pps=10</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-gua-sha-and-jade-gua-sha-facial-massage-tool-set/p/6068311?productId=6068311&amp;pps=11</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-sodalite-gua-sha-massage-tool-rabbit-ear-shape/p/6068293?productId=6068293&amp;pps=12</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/wahl-3-in-1-full-back-sheet-cushion/p/888649?productId=888649&amp;pps=13</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-black-obsidian-facial-roller-and-comb-edge-gua-sha-massage-tool-set/p/6068302?productId=6068302&amp;pps=14</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-black-obsidian-spoon-shape-gua-sha-massage-tool/p/6068304?productId=6068304&amp;pps=15</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-black-obsidian-facal-roller-and-massager/p/4146674?productId=4146674&amp;pps=16</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/casaveda-kansa-bronze-ayurveda-face-massage-roller-skin-brightening/p/8231756?productId=8231756&amp;pps=17</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/the-rolling-concept-jade-facial-roller-1pc/p/664466?productId=664466&amp;pps=18</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/callesta-jade-roller-facial-massage-roller/p/853495?productId=853495&amp;pps=19</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-gua-sha-mushroom-gua-sha-and-teeth-eadge-gua-sha-massage-tool-set/p/6068313?productId=6068313&amp;pps=20</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-jade-face-roller-and-mushroom-gua-sha-facial-massage-tool-set/p/6068309?productId=6068309&amp;pps=1</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-green-jade-wing-shape-gua-sha-facial-massage-tool/p/6068295?productId=6068295&amp;pps=2</t>
+  </si>
+  <si>
+    <t>2026-09-15T17:41:50.897Z</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-jade-face-roller-and-leaf-shape-gua-sha-massage-tool-set/p/6068324?productId=6068324&amp;pps=3</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-face-roller-for-nose-and-neck/p/14018031?productId=14018031&amp;pps=4</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-black-obsidian-leaf-rabbit-ear-and-teeth-edge-shape-gua-sha-massage-tool-set/p/6068315?productId=6068315&amp;pps=5</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-white-opalite-facial-roller/p/4146677?productId=4146677&amp;pps=6</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/bungalow-beauty-gold-and-green-jade-roller/p/19939784?productId=19939784&amp;pps=7</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-green-aventurine-jade-facial-roller/p/4146676?productId=4146676&amp;pps=8</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/riyo-herbs-jade-face-roller-massager/p/5065833?productId=5065833&amp;pps=9</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/zoe-ayla-black-obsidian-extravagant-facialroller-noiseless/p/5679095?productId=5679095&amp;pps=10</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-black-obsidian-wing-shape-gua-sha-facial-massage-tool/p/6068297?productId=6068297&amp;pps=11</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-black-obsidian-face-roller-and-mushroom-gua-sha-facial-massage-tool/p/6068310?productId=6068310&amp;pps=12</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-black-obsidian-leaf-shape-rabbit-ear-shape-gua-sha-facial-massage-tool/p/6068318?productId=6068318&amp;pps=13</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-black-obsidian-face-roller-and-wing-shape-gua-sha-massage-tool-set/p/6068298?productId=6068298&amp;pps=14</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-black-obsidian-mushroom-gua-sha-tool/p/4146682?productId=4146682&amp;pps=15</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-face-roller-and-teeth-shape-gua-sha-set/p/4146692?productId=4146692&amp;pps=16</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-jade-leaf-rabbit-ear-and-teeth-edge-shape-gua-sha-massage-tool-set/p/6068319?productId=6068319&amp;pps=17</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-black-obsidian-mushroom-and-rabbit-ear-shape-gua-sha-massage-tool-set/p/6068317?productId=6068317&amp;pps=18</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-face-roller-and-rabbit-ear-shape-gua-sha-massage-tool-set/p/6068323?productId=6068323&amp;pps=19</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-jade-face-roller-and-rose-quartz-facial-roller-set/p/6068330?productId=6068330&amp;pps=20</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-rose-quartz-face-roller-and-gua-sha-set-with-jade-face-roller-and-gua-sha-set/p/4146673?productId=4146673&amp;pps=1</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-massage-tools-set/p/6068328?productId=6068328&amp;pps=2</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-massage-tool-set/p/6068322?productId=6068322&amp;pps=3</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-black-obsidian-rabbit-ear-and-teeth-eadge-gua-sha-massage-tool-set/p/6068316?productId=6068316&amp;pps=4</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-jade-face-roller-and-rabbit-ear-shape-gua-sha-massage-tool-set/p/6068326?productId=6068326&amp;pps=5</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/agaro-scalp-massager-rechargeable-electric-head-kneading-massager/p/19030384?productId=19030384&amp;pps=6</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/bronson-professional-ice-facial-roller-for-face-eye-neck-and-body-facial-skin-care-tool-for-women/p/9043050?productId=9043050&amp;pps=7</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/agaro-scalp-massager-rechargeable-electric-head-kneading-massager-3-speed-modes/p/20799860?productId=20799860&amp;pps=8</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/agaro-led-hair-therapy-comb-red-blue-light-vibration-massage-reduces-hair-fall-boosts-growth/p/23447162?productId=23447162&amp;pps=9</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/venihea-chhota-natkhat-personal-full-body-massager/p/18306771?productId=18306771&amp;pps=10</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/ras-luxury-oils-rose-quartz-facial-roller-1pc/p/637570?productId=637570&amp;pps=11</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/bronson-professional-5-in-1-body-and-face-compact-beauty-care-massage-and-exfoliation-tool/p/337494?productId=337494&amp;pps=12</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/azah-personal-care-massager-for-women-fuschia-pink-color/p/5069600?productId=5069600&amp;pps=13</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/beardo-sport-deep-tissue-massage-gun-4-hour-run-time-99-modes/p/19407732?productId=19407732&amp;pps=14</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/scalppie-hair-scalp-oil-applicator-white/p/19010999?productId=19010999&amp;pps=15</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/vandelay-mini-mate-massager-wireless-waterproof-personal-body-massager-black/p/5167150?productId=5167150&amp;pps=16</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/hector-professional-foot-spa-massager-with-8l-capacity/p/20516782?productId=20516782&amp;pps=17</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/house-of-beauty-3d-face-massager/p/1484937?productId=1484937&amp;pps=18</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/vandelay-magic-mate-rechargeable-personal-body-massager-for-women-men-waterproof-cherry-pink/p/5167145?productId=5167145&amp;pps=19</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/nykaa-naturals-ice-roller-for-de-puffing-and-face-toning-massage/p/5337838?productId=5337838&amp;pps=20</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/semino-automatic-electric-lip-plumper-enhancement-device/p/12408934?productId=12408934&amp;pps=1</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/beardo-stress-buster-electric-scalp-massager-120-min-run-time-3-speed-modes/p/19407731?productId=19407731&amp;pps=2</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/venihea-hulk-full-body-personal-massager-spicy-pink/p/18306773?productId=18306773&amp;pps=3</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/nykaa-naturals-ice-roller-for-de-puffing-and-face-toning-massage/p/5337838?productId=5337838&amp;skuId=1485845&amp;pps=4</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/agaro-marvel-electric-h-and-held-full-body-hammer-massager/p/758188?productId=758188&amp;pps=5</t>
+  </si>
+  <si>
+    <t>2026-09-15T17:41:50.898Z</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/house-of-beauty-ice-globe-pink-cryo-facial/p/930212?productId=930212&amp;pps=6</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/azah-rose-quartz-face-roller-gua-sha-set/p/5881753?productId=5881753&amp;pps=7</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/bronson-professional-body-massager-gun-with-4-massage-heads/p/11859517?productId=11859517&amp;pps=8</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-ice-roller-for-face-eye-2-in-1-puffiness-migraine-pain-relief-facial-ice-roller/p/8845072?productId=8845072&amp;pps=9</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/lifelong-llm45-rechargeable-tapping-body-massager-brown/p/809564?productId=809564&amp;pps=10</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/mymuse-groove-full-body-massager-lemon-tart/p/10303614?productId=10303614&amp;pps=11</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-oil-absorbing-volcanic-roller-reusable-portable-oily-skin-control-roller/p/7828603?productId=7828603&amp;pps=12</t>
+  </si>
+  <si>
+    <t>https://www.nykaa.com/getmecraft-ice-facial-roller-for-face-and-eye-silicone-ice-mold-for-facial-skin-care-tool-for-women/p/6937991?productId=6937991&amp;pps=13</t>
   </si>
 </sst>
 </file>
@@ -423,7 +1374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E314"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
@@ -487,21 +1438,4347 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>65</v>
+      </c>
+      <c r="B57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>68</v>
+      </c>
+      <c r="B60" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>70</v>
+      </c>
+      <c r="B62" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>72</v>
+      </c>
+      <c r="B64" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>73</v>
+      </c>
+      <c r="B65" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>74</v>
+      </c>
+      <c r="B66" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>75</v>
+      </c>
+      <c r="B67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>77</v>
+      </c>
+      <c r="B69" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" t="s">
+        <v>7</v>
+      </c>
+      <c r="D72" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" t="s">
+        <v>7</v>
+      </c>
+      <c r="D73" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>86</v>
+      </c>
+      <c r="B78" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" t="s">
+        <v>7</v>
+      </c>
+      <c r="D78" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>87</v>
+      </c>
+      <c r="B79" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>88</v>
+      </c>
+      <c r="B80" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" t="s">
+        <v>7</v>
+      </c>
+      <c r="D80" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>89</v>
+      </c>
+      <c r="B81" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" t="s">
+        <v>7</v>
+      </c>
+      <c r="D81" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>90</v>
+      </c>
+      <c r="B82" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" t="s">
+        <v>7</v>
+      </c>
+      <c r="D82" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>91</v>
+      </c>
+      <c r="B83" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" t="s">
+        <v>7</v>
+      </c>
+      <c r="D83" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>92</v>
+      </c>
+      <c r="B84" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>93</v>
+      </c>
+      <c r="B85" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>94</v>
+      </c>
+      <c r="B86" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" t="s">
+        <v>7</v>
+      </c>
+      <c r="D86" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>95</v>
+      </c>
+      <c r="B87" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" t="s">
+        <v>7</v>
+      </c>
+      <c r="D87" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>96</v>
+      </c>
+      <c r="B88" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" t="s">
+        <v>7</v>
+      </c>
+      <c r="D88" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>97</v>
+      </c>
+      <c r="B89" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>98</v>
+      </c>
+      <c r="B90" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" t="s">
+        <v>7</v>
+      </c>
+      <c r="D90" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>99</v>
+      </c>
+      <c r="B91" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>100</v>
+      </c>
+      <c r="B92" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" t="s">
+        <v>7</v>
+      </c>
+      <c r="D92" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>101</v>
+      </c>
+      <c r="B93" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" t="s">
+        <v>7</v>
+      </c>
+      <c r="D93" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" t="s">
+        <v>7</v>
+      </c>
+      <c r="D94" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>103</v>
+      </c>
+      <c r="B95" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" t="s">
+        <v>7</v>
+      </c>
+      <c r="D95" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>104</v>
+      </c>
+      <c r="B96" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" t="s">
+        <v>7</v>
+      </c>
+      <c r="D96" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>105</v>
+      </c>
+      <c r="B97" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" t="s">
+        <v>7</v>
+      </c>
+      <c r="D97" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>106</v>
+      </c>
+      <c r="B98" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" t="s">
+        <v>7</v>
+      </c>
+      <c r="D98" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>107</v>
+      </c>
+      <c r="B99" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" t="s">
+        <v>7</v>
+      </c>
+      <c r="D99" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>108</v>
+      </c>
+      <c r="B100" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" t="s">
+        <v>7</v>
+      </c>
+      <c r="D100" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>109</v>
+      </c>
+      <c r="B101" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" t="s">
+        <v>7</v>
+      </c>
+      <c r="D101" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>110</v>
+      </c>
+      <c r="B102" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" t="s">
+        <v>7</v>
+      </c>
+      <c r="D102" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>111</v>
+      </c>
+      <c r="B103" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" t="s">
+        <v>7</v>
+      </c>
+      <c r="D103" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>112</v>
+      </c>
+      <c r="B104" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" t="s">
+        <v>7</v>
+      </c>
+      <c r="D104" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>113</v>
+      </c>
+      <c r="B105" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" t="s">
+        <v>7</v>
+      </c>
+      <c r="D105" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>114</v>
+      </c>
+      <c r="B106" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" t="s">
+        <v>7</v>
+      </c>
+      <c r="D106" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>115</v>
+      </c>
+      <c r="B107" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" t="s">
+        <v>7</v>
+      </c>
+      <c r="D107" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>116</v>
+      </c>
+      <c r="B108" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108" t="s">
+        <v>7</v>
+      </c>
+      <c r="D108" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>117</v>
+      </c>
+      <c r="B109" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" t="s">
+        <v>7</v>
+      </c>
+      <c r="D109" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>118</v>
+      </c>
+      <c r="B110" t="s">
+        <v>6</v>
+      </c>
+      <c r="C110" t="s">
+        <v>7</v>
+      </c>
+      <c r="D110" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>119</v>
+      </c>
+      <c r="B111" t="s">
+        <v>6</v>
+      </c>
+      <c r="C111" t="s">
+        <v>7</v>
+      </c>
+      <c r="D111" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>120</v>
+      </c>
+      <c r="B112" t="s">
+        <v>6</v>
+      </c>
+      <c r="C112" t="s">
+        <v>7</v>
+      </c>
+      <c r="D112" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>121</v>
+      </c>
+      <c r="B113" t="s">
+        <v>6</v>
+      </c>
+      <c r="C113" t="s">
+        <v>7</v>
+      </c>
+      <c r="D113" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>122</v>
+      </c>
+      <c r="B114" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" t="s">
+        <v>7</v>
+      </c>
+      <c r="D114" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>123</v>
+      </c>
+      <c r="B115" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" t="s">
+        <v>7</v>
+      </c>
+      <c r="D115" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>124</v>
+      </c>
+      <c r="B116" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" t="s">
+        <v>7</v>
+      </c>
+      <c r="D116" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>125</v>
+      </c>
+      <c r="B117" t="s">
+        <v>6</v>
+      </c>
+      <c r="C117" t="s">
+        <v>7</v>
+      </c>
+      <c r="D117" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>126</v>
+      </c>
+      <c r="B118" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118" t="s">
+        <v>7</v>
+      </c>
+      <c r="D118" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>128</v>
+      </c>
+      <c r="B119" t="s">
+        <v>6</v>
+      </c>
+      <c r="C119" t="s">
+        <v>7</v>
+      </c>
+      <c r="D119" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>129</v>
+      </c>
+      <c r="B120" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120" t="s">
+        <v>7</v>
+      </c>
+      <c r="D120" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>130</v>
+      </c>
+      <c r="B121" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" t="s">
+        <v>7</v>
+      </c>
+      <c r="D121" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>131</v>
+      </c>
+      <c r="B122" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" t="s">
+        <v>7</v>
+      </c>
+      <c r="D122" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>132</v>
+      </c>
+      <c r="B123" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" t="s">
+        <v>7</v>
+      </c>
+      <c r="D123" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>133</v>
+      </c>
+      <c r="B124" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" t="s">
+        <v>7</v>
+      </c>
+      <c r="D124" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>134</v>
+      </c>
+      <c r="B125" t="s">
+        <v>6</v>
+      </c>
+      <c r="C125" t="s">
+        <v>7</v>
+      </c>
+      <c r="D125" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>135</v>
+      </c>
+      <c r="B126" t="s">
+        <v>6</v>
+      </c>
+      <c r="C126" t="s">
+        <v>7</v>
+      </c>
+      <c r="D126" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>136</v>
+      </c>
+      <c r="B127" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" t="s">
+        <v>7</v>
+      </c>
+      <c r="D127" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>137</v>
+      </c>
+      <c r="B128" t="s">
+        <v>6</v>
+      </c>
+      <c r="C128" t="s">
+        <v>7</v>
+      </c>
+      <c r="D128" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>138</v>
+      </c>
+      <c r="B129" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" t="s">
+        <v>7</v>
+      </c>
+      <c r="D129" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>139</v>
+      </c>
+      <c r="B130" t="s">
+        <v>6</v>
+      </c>
+      <c r="C130" t="s">
+        <v>7</v>
+      </c>
+      <c r="D130" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>140</v>
+      </c>
+      <c r="B131" t="s">
+        <v>6</v>
+      </c>
+      <c r="C131" t="s">
+        <v>7</v>
+      </c>
+      <c r="D131" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>141</v>
+      </c>
+      <c r="B132" t="s">
+        <v>6</v>
+      </c>
+      <c r="C132" t="s">
+        <v>7</v>
+      </c>
+      <c r="D132" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>142</v>
+      </c>
+      <c r="B133" t="s">
+        <v>6</v>
+      </c>
+      <c r="C133" t="s">
+        <v>7</v>
+      </c>
+      <c r="D133" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>143</v>
+      </c>
+      <c r="B134" t="s">
+        <v>6</v>
+      </c>
+      <c r="C134" t="s">
+        <v>7</v>
+      </c>
+      <c r="D134" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>144</v>
+      </c>
+      <c r="B135" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" t="s">
+        <v>7</v>
+      </c>
+      <c r="D135" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>145</v>
+      </c>
+      <c r="B136" t="s">
+        <v>6</v>
+      </c>
+      <c r="C136" t="s">
+        <v>7</v>
+      </c>
+      <c r="D136" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>146</v>
+      </c>
+      <c r="B137" t="s">
+        <v>6</v>
+      </c>
+      <c r="C137" t="s">
+        <v>7</v>
+      </c>
+      <c r="D137" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>147</v>
+      </c>
+      <c r="B138" t="s">
+        <v>6</v>
+      </c>
+      <c r="C138" t="s">
+        <v>7</v>
+      </c>
+      <c r="D138" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>148</v>
+      </c>
+      <c r="B139" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" t="s">
+        <v>7</v>
+      </c>
+      <c r="D139" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>149</v>
+      </c>
+      <c r="B140" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" t="s">
+        <v>7</v>
+      </c>
+      <c r="D140" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>150</v>
+      </c>
+      <c r="B141" t="s">
+        <v>6</v>
+      </c>
+      <c r="C141" t="s">
+        <v>7</v>
+      </c>
+      <c r="D141" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>151</v>
+      </c>
+      <c r="B142" t="s">
+        <v>6</v>
+      </c>
+      <c r="C142" t="s">
+        <v>7</v>
+      </c>
+      <c r="D142" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>152</v>
+      </c>
+      <c r="B143" t="s">
+        <v>6</v>
+      </c>
+      <c r="C143" t="s">
+        <v>7</v>
+      </c>
+      <c r="D143" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>153</v>
+      </c>
+      <c r="B144" t="s">
+        <v>6</v>
+      </c>
+      <c r="C144" t="s">
+        <v>7</v>
+      </c>
+      <c r="D144" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>154</v>
+      </c>
+      <c r="B145" t="s">
+        <v>6</v>
+      </c>
+      <c r="C145" t="s">
+        <v>7</v>
+      </c>
+      <c r="D145" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>155</v>
+      </c>
+      <c r="B146" t="s">
+        <v>6</v>
+      </c>
+      <c r="C146" t="s">
+        <v>7</v>
+      </c>
+      <c r="D146" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>156</v>
+      </c>
+      <c r="B147" t="s">
+        <v>6</v>
+      </c>
+      <c r="C147" t="s">
+        <v>7</v>
+      </c>
+      <c r="D147" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>157</v>
+      </c>
+      <c r="B148" t="s">
+        <v>6</v>
+      </c>
+      <c r="C148" t="s">
+        <v>7</v>
+      </c>
+      <c r="D148" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>158</v>
+      </c>
+      <c r="B149" t="s">
+        <v>6</v>
+      </c>
+      <c r="C149" t="s">
+        <v>7</v>
+      </c>
+      <c r="D149" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>159</v>
+      </c>
+      <c r="B150" t="s">
+        <v>6</v>
+      </c>
+      <c r="C150" t="s">
+        <v>7</v>
+      </c>
+      <c r="D150" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>160</v>
+      </c>
+      <c r="B151" t="s">
+        <v>6</v>
+      </c>
+      <c r="C151" t="s">
+        <v>7</v>
+      </c>
+      <c r="D151" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>161</v>
+      </c>
+      <c r="B152" t="s">
+        <v>6</v>
+      </c>
+      <c r="C152" t="s">
+        <v>7</v>
+      </c>
+      <c r="D152" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>162</v>
+      </c>
+      <c r="B153" t="s">
+        <v>6</v>
+      </c>
+      <c r="C153" t="s">
+        <v>7</v>
+      </c>
+      <c r="D153" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>163</v>
+      </c>
+      <c r="B154" t="s">
+        <v>6</v>
+      </c>
+      <c r="C154" t="s">
+        <v>7</v>
+      </c>
+      <c r="D154" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>165</v>
+      </c>
+      <c r="B155" t="s">
+        <v>6</v>
+      </c>
+      <c r="C155" t="s">
+        <v>7</v>
+      </c>
+      <c r="D155" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>166</v>
+      </c>
+      <c r="B156" t="s">
+        <v>6</v>
+      </c>
+      <c r="C156" t="s">
+        <v>7</v>
+      </c>
+      <c r="D156" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>167</v>
+      </c>
+      <c r="B157" t="s">
+        <v>6</v>
+      </c>
+      <c r="C157" t="s">
+        <v>7</v>
+      </c>
+      <c r="D157" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>168</v>
+      </c>
+      <c r="B158" t="s">
+        <v>6</v>
+      </c>
+      <c r="C158" t="s">
+        <v>7</v>
+      </c>
+      <c r="D158" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>169</v>
+      </c>
+      <c r="B159" t="s">
+        <v>6</v>
+      </c>
+      <c r="C159" t="s">
+        <v>7</v>
+      </c>
+      <c r="D159" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>170</v>
+      </c>
+      <c r="B160" t="s">
+        <v>6</v>
+      </c>
+      <c r="C160" t="s">
+        <v>7</v>
+      </c>
+      <c r="D160" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>171</v>
+      </c>
+      <c r="B161" t="s">
+        <v>6</v>
+      </c>
+      <c r="C161" t="s">
+        <v>7</v>
+      </c>
+      <c r="D161" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>172</v>
+      </c>
+      <c r="B162" t="s">
+        <v>6</v>
+      </c>
+      <c r="C162" t="s">
+        <v>7</v>
+      </c>
+      <c r="D162" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>173</v>
+      </c>
+      <c r="B163" t="s">
+        <v>6</v>
+      </c>
+      <c r="C163" t="s">
+        <v>7</v>
+      </c>
+      <c r="D163" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>174</v>
+      </c>
+      <c r="B164" t="s">
+        <v>6</v>
+      </c>
+      <c r="C164" t="s">
+        <v>7</v>
+      </c>
+      <c r="D164" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>175</v>
+      </c>
+      <c r="B165" t="s">
+        <v>6</v>
+      </c>
+      <c r="C165" t="s">
+        <v>7</v>
+      </c>
+      <c r="D165" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>176</v>
+      </c>
+      <c r="B166" t="s">
+        <v>6</v>
+      </c>
+      <c r="C166" t="s">
+        <v>7</v>
+      </c>
+      <c r="D166" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>177</v>
+      </c>
+      <c r="B167" t="s">
+        <v>6</v>
+      </c>
+      <c r="C167" t="s">
+        <v>7</v>
+      </c>
+      <c r="D167" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>178</v>
+      </c>
+      <c r="B168" t="s">
+        <v>6</v>
+      </c>
+      <c r="C168" t="s">
+        <v>7</v>
+      </c>
+      <c r="D168" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>179</v>
+      </c>
+      <c r="B169" t="s">
+        <v>6</v>
+      </c>
+      <c r="C169" t="s">
+        <v>7</v>
+      </c>
+      <c r="D169" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>180</v>
+      </c>
+      <c r="B170" t="s">
+        <v>6</v>
+      </c>
+      <c r="C170" t="s">
+        <v>7</v>
+      </c>
+      <c r="D170" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>181</v>
+      </c>
+      <c r="B171" t="s">
+        <v>6</v>
+      </c>
+      <c r="C171" t="s">
+        <v>7</v>
+      </c>
+      <c r="D171" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>182</v>
+      </c>
+      <c r="B172" t="s">
+        <v>6</v>
+      </c>
+      <c r="C172" t="s">
+        <v>7</v>
+      </c>
+      <c r="D172" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>183</v>
+      </c>
+      <c r="B173" t="s">
+        <v>6</v>
+      </c>
+      <c r="C173" t="s">
+        <v>7</v>
+      </c>
+      <c r="D173" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>184</v>
+      </c>
+      <c r="B174" t="s">
+        <v>6</v>
+      </c>
+      <c r="C174" t="s">
+        <v>7</v>
+      </c>
+      <c r="D174" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>185</v>
+      </c>
+      <c r="B175" t="s">
+        <v>6</v>
+      </c>
+      <c r="C175" t="s">
+        <v>7</v>
+      </c>
+      <c r="D175" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>186</v>
+      </c>
+      <c r="B176" t="s">
+        <v>6</v>
+      </c>
+      <c r="C176" t="s">
+        <v>7</v>
+      </c>
+      <c r="D176" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>187</v>
+      </c>
+      <c r="B177" t="s">
+        <v>6</v>
+      </c>
+      <c r="C177" t="s">
+        <v>7</v>
+      </c>
+      <c r="D177" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>188</v>
+      </c>
+      <c r="B178" t="s">
+        <v>6</v>
+      </c>
+      <c r="C178" t="s">
+        <v>7</v>
+      </c>
+      <c r="D178" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>189</v>
+      </c>
+      <c r="B179" t="s">
+        <v>6</v>
+      </c>
+      <c r="C179" t="s">
+        <v>7</v>
+      </c>
+      <c r="D179" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>190</v>
+      </c>
+      <c r="B180" t="s">
+        <v>6</v>
+      </c>
+      <c r="C180" t="s">
+        <v>7</v>
+      </c>
+      <c r="D180" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>191</v>
+      </c>
+      <c r="B181" t="s">
+        <v>6</v>
+      </c>
+      <c r="C181" t="s">
+        <v>7</v>
+      </c>
+      <c r="D181" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>192</v>
+      </c>
+      <c r="B182" t="s">
+        <v>6</v>
+      </c>
+      <c r="C182" t="s">
+        <v>7</v>
+      </c>
+      <c r="D182" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>193</v>
+      </c>
+      <c r="B183" t="s">
+        <v>6</v>
+      </c>
+      <c r="C183" t="s">
+        <v>7</v>
+      </c>
+      <c r="D183" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>194</v>
+      </c>
+      <c r="B184" t="s">
+        <v>6</v>
+      </c>
+      <c r="C184" t="s">
+        <v>7</v>
+      </c>
+      <c r="D184" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>195</v>
+      </c>
+      <c r="B185" t="s">
+        <v>6</v>
+      </c>
+      <c r="C185" t="s">
+        <v>7</v>
+      </c>
+      <c r="D185" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>196</v>
+      </c>
+      <c r="B186" t="s">
+        <v>6</v>
+      </c>
+      <c r="C186" t="s">
+        <v>7</v>
+      </c>
+      <c r="D186" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>197</v>
+      </c>
+      <c r="B187" t="s">
+        <v>6</v>
+      </c>
+      <c r="C187" t="s">
+        <v>7</v>
+      </c>
+      <c r="D187" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>198</v>
+      </c>
+      <c r="B188" t="s">
+        <v>6</v>
+      </c>
+      <c r="C188" t="s">
+        <v>7</v>
+      </c>
+      <c r="D188" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>199</v>
+      </c>
+      <c r="B189" t="s">
+        <v>6</v>
+      </c>
+      <c r="C189" t="s">
+        <v>7</v>
+      </c>
+      <c r="D189" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>200</v>
+      </c>
+      <c r="B190" t="s">
+        <v>6</v>
+      </c>
+      <c r="C190" t="s">
+        <v>7</v>
+      </c>
+      <c r="D190" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>201</v>
+      </c>
+      <c r="B191" t="s">
+        <v>6</v>
+      </c>
+      <c r="C191" t="s">
+        <v>7</v>
+      </c>
+      <c r="D191" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>202</v>
+      </c>
+      <c r="B192" t="s">
+        <v>6</v>
+      </c>
+      <c r="C192" t="s">
+        <v>7</v>
+      </c>
+      <c r="D192" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>203</v>
+      </c>
+      <c r="B193" t="s">
+        <v>6</v>
+      </c>
+      <c r="C193" t="s">
+        <v>7</v>
+      </c>
+      <c r="D193" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>204</v>
+      </c>
+      <c r="B194" t="s">
+        <v>6</v>
+      </c>
+      <c r="C194" t="s">
+        <v>7</v>
+      </c>
+      <c r="D194" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>206</v>
+      </c>
+      <c r="B195" t="s">
+        <v>6</v>
+      </c>
+      <c r="C195" t="s">
+        <v>7</v>
+      </c>
+      <c r="D195" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>207</v>
+      </c>
+      <c r="B196" t="s">
+        <v>6</v>
+      </c>
+      <c r="C196" t="s">
+        <v>7</v>
+      </c>
+      <c r="D196" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>208</v>
+      </c>
+      <c r="B197" t="s">
+        <v>6</v>
+      </c>
+      <c r="C197" t="s">
+        <v>7</v>
+      </c>
+      <c r="D197" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>209</v>
+      </c>
+      <c r="B198" t="s">
+        <v>6</v>
+      </c>
+      <c r="C198" t="s">
+        <v>7</v>
+      </c>
+      <c r="D198" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>210</v>
+      </c>
+      <c r="B199" t="s">
+        <v>6</v>
+      </c>
+      <c r="C199" t="s">
+        <v>7</v>
+      </c>
+      <c r="D199" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>211</v>
+      </c>
+      <c r="B200" t="s">
+        <v>6</v>
+      </c>
+      <c r="C200" t="s">
+        <v>7</v>
+      </c>
+      <c r="D200" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>212</v>
+      </c>
+      <c r="B201" t="s">
+        <v>6</v>
+      </c>
+      <c r="C201" t="s">
+        <v>7</v>
+      </c>
+      <c r="D201" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>213</v>
+      </c>
+      <c r="B202" t="s">
+        <v>6</v>
+      </c>
+      <c r="C202" t="s">
+        <v>7</v>
+      </c>
+      <c r="D202" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>214</v>
+      </c>
+      <c r="B203" t="s">
+        <v>6</v>
+      </c>
+      <c r="C203" t="s">
+        <v>7</v>
+      </c>
+      <c r="D203" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>215</v>
+      </c>
+      <c r="B204" t="s">
+        <v>6</v>
+      </c>
+      <c r="C204" t="s">
+        <v>7</v>
+      </c>
+      <c r="D204" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>216</v>
+      </c>
+      <c r="B205" t="s">
+        <v>6</v>
+      </c>
+      <c r="C205" t="s">
+        <v>7</v>
+      </c>
+      <c r="D205" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>217</v>
+      </c>
+      <c r="B206" t="s">
+        <v>6</v>
+      </c>
+      <c r="C206" t="s">
+        <v>7</v>
+      </c>
+      <c r="D206" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>218</v>
+      </c>
+      <c r="B207" t="s">
+        <v>6</v>
+      </c>
+      <c r="C207" t="s">
+        <v>7</v>
+      </c>
+      <c r="D207" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>219</v>
+      </c>
+      <c r="B208" t="s">
+        <v>6</v>
+      </c>
+      <c r="C208" t="s">
+        <v>7</v>
+      </c>
+      <c r="D208" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>220</v>
+      </c>
+      <c r="B209" t="s">
+        <v>6</v>
+      </c>
+      <c r="C209" t="s">
+        <v>7</v>
+      </c>
+      <c r="D209" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>221</v>
+      </c>
+      <c r="B210" t="s">
+        <v>6</v>
+      </c>
+      <c r="C210" t="s">
+        <v>7</v>
+      </c>
+      <c r="D210" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>222</v>
+      </c>
+      <c r="B211" t="s">
+        <v>6</v>
+      </c>
+      <c r="C211" t="s">
+        <v>7</v>
+      </c>
+      <c r="D211" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>223</v>
+      </c>
+      <c r="B212" t="s">
+        <v>6</v>
+      </c>
+      <c r="C212" t="s">
+        <v>7</v>
+      </c>
+      <c r="D212" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>224</v>
+      </c>
+      <c r="B213" t="s">
+        <v>6</v>
+      </c>
+      <c r="C213" t="s">
+        <v>7</v>
+      </c>
+      <c r="D213" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>225</v>
+      </c>
+      <c r="B214" t="s">
+        <v>6</v>
+      </c>
+      <c r="C214" t="s">
+        <v>7</v>
+      </c>
+      <c r="D214" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>226</v>
+      </c>
+      <c r="B215" t="s">
+        <v>6</v>
+      </c>
+      <c r="C215" t="s">
+        <v>7</v>
+      </c>
+      <c r="D215" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>227</v>
+      </c>
+      <c r="B216" t="s">
+        <v>6</v>
+      </c>
+      <c r="C216" t="s">
+        <v>7</v>
+      </c>
+      <c r="D216" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>228</v>
+      </c>
+      <c r="B217" t="s">
+        <v>6</v>
+      </c>
+      <c r="C217" t="s">
+        <v>7</v>
+      </c>
+      <c r="D217" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>229</v>
+      </c>
+      <c r="B218" t="s">
+        <v>6</v>
+      </c>
+      <c r="C218" t="s">
+        <v>7</v>
+      </c>
+      <c r="D218" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>230</v>
+      </c>
+      <c r="B219" t="s">
+        <v>6</v>
+      </c>
+      <c r="C219" t="s">
+        <v>7</v>
+      </c>
+      <c r="D219" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>231</v>
+      </c>
+      <c r="B220" t="s">
+        <v>6</v>
+      </c>
+      <c r="C220" t="s">
+        <v>7</v>
+      </c>
+      <c r="D220" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>232</v>
+      </c>
+      <c r="B221" t="s">
+        <v>6</v>
+      </c>
+      <c r="C221" t="s">
+        <v>7</v>
+      </c>
+      <c r="D221" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>233</v>
+      </c>
+      <c r="B222" t="s">
+        <v>6</v>
+      </c>
+      <c r="C222" t="s">
+        <v>7</v>
+      </c>
+      <c r="D222" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>235</v>
+      </c>
+      <c r="B223" t="s">
+        <v>6</v>
+      </c>
+      <c r="C223" t="s">
+        <v>7</v>
+      </c>
+      <c r="D223" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>236</v>
+      </c>
+      <c r="B224" t="s">
+        <v>6</v>
+      </c>
+      <c r="C224" t="s">
+        <v>7</v>
+      </c>
+      <c r="D224" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>237</v>
+      </c>
+      <c r="B225" t="s">
+        <v>6</v>
+      </c>
+      <c r="C225" t="s">
+        <v>7</v>
+      </c>
+      <c r="D225" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>238</v>
+      </c>
+      <c r="B226" t="s">
+        <v>6</v>
+      </c>
+      <c r="C226" t="s">
+        <v>7</v>
+      </c>
+      <c r="D226" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>239</v>
+      </c>
+      <c r="B227" t="s">
+        <v>6</v>
+      </c>
+      <c r="C227" t="s">
+        <v>7</v>
+      </c>
+      <c r="D227" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>240</v>
+      </c>
+      <c r="B228" t="s">
+        <v>6</v>
+      </c>
+      <c r="C228" t="s">
+        <v>7</v>
+      </c>
+      <c r="D228" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>241</v>
+      </c>
+      <c r="B229" t="s">
+        <v>6</v>
+      </c>
+      <c r="C229" t="s">
+        <v>7</v>
+      </c>
+      <c r="D229" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>242</v>
+      </c>
+      <c r="B230" t="s">
+        <v>6</v>
+      </c>
+      <c r="C230" t="s">
+        <v>7</v>
+      </c>
+      <c r="D230" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>243</v>
+      </c>
+      <c r="B231" t="s">
+        <v>6</v>
+      </c>
+      <c r="C231" t="s">
+        <v>7</v>
+      </c>
+      <c r="D231" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>244</v>
+      </c>
+      <c r="B232" t="s">
+        <v>6</v>
+      </c>
+      <c r="C232" t="s">
+        <v>7</v>
+      </c>
+      <c r="D232" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>245</v>
+      </c>
+      <c r="B233" t="s">
+        <v>6</v>
+      </c>
+      <c r="C233" t="s">
+        <v>7</v>
+      </c>
+      <c r="D233" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>246</v>
+      </c>
+      <c r="B234" t="s">
+        <v>6</v>
+      </c>
+      <c r="C234" t="s">
+        <v>7</v>
+      </c>
+      <c r="D234" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>247</v>
+      </c>
+      <c r="B235" t="s">
+        <v>6</v>
+      </c>
+      <c r="C235" t="s">
+        <v>7</v>
+      </c>
+      <c r="D235" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>248</v>
+      </c>
+      <c r="B236" t="s">
+        <v>6</v>
+      </c>
+      <c r="C236" t="s">
+        <v>7</v>
+      </c>
+      <c r="D236" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>249</v>
+      </c>
+      <c r="B237" t="s">
+        <v>6</v>
+      </c>
+      <c r="C237" t="s">
+        <v>7</v>
+      </c>
+      <c r="D237" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>250</v>
+      </c>
+      <c r="B238" t="s">
+        <v>6</v>
+      </c>
+      <c r="C238" t="s">
+        <v>7</v>
+      </c>
+      <c r="D238" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>251</v>
+      </c>
+      <c r="B239" t="s">
+        <v>6</v>
+      </c>
+      <c r="C239" t="s">
+        <v>7</v>
+      </c>
+      <c r="D239" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>252</v>
+      </c>
+      <c r="B240" t="s">
+        <v>6</v>
+      </c>
+      <c r="C240" t="s">
+        <v>7</v>
+      </c>
+      <c r="D240" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>253</v>
+      </c>
+      <c r="B241" t="s">
+        <v>6</v>
+      </c>
+      <c r="C241" t="s">
+        <v>7</v>
+      </c>
+      <c r="D241" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>254</v>
+      </c>
+      <c r="B242" t="s">
+        <v>6</v>
+      </c>
+      <c r="C242" t="s">
+        <v>7</v>
+      </c>
+      <c r="D242" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>255</v>
+      </c>
+      <c r="B243" t="s">
+        <v>6</v>
+      </c>
+      <c r="C243" t="s">
+        <v>7</v>
+      </c>
+      <c r="D243" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>256</v>
+      </c>
+      <c r="B244" t="s">
+        <v>6</v>
+      </c>
+      <c r="C244" t="s">
+        <v>7</v>
+      </c>
+      <c r="D244" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>257</v>
+      </c>
+      <c r="B245" t="s">
+        <v>6</v>
+      </c>
+      <c r="C245" t="s">
+        <v>7</v>
+      </c>
+      <c r="D245" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>258</v>
+      </c>
+      <c r="B246" t="s">
+        <v>6</v>
+      </c>
+      <c r="C246" t="s">
+        <v>7</v>
+      </c>
+      <c r="D246" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>259</v>
+      </c>
+      <c r="B247" t="s">
+        <v>6</v>
+      </c>
+      <c r="C247" t="s">
+        <v>7</v>
+      </c>
+      <c r="D247" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>260</v>
+      </c>
+      <c r="B248" t="s">
+        <v>6</v>
+      </c>
+      <c r="C248" t="s">
+        <v>7</v>
+      </c>
+      <c r="D248" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>261</v>
+      </c>
+      <c r="B249" t="s">
+        <v>6</v>
+      </c>
+      <c r="C249" t="s">
+        <v>7</v>
+      </c>
+      <c r="D249" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>262</v>
+      </c>
+      <c r="B250" t="s">
+        <v>6</v>
+      </c>
+      <c r="C250" t="s">
+        <v>7</v>
+      </c>
+      <c r="D250" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>263</v>
+      </c>
+      <c r="B251" t="s">
+        <v>6</v>
+      </c>
+      <c r="C251" t="s">
+        <v>7</v>
+      </c>
+      <c r="D251" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>264</v>
+      </c>
+      <c r="B252" t="s">
+        <v>6</v>
+      </c>
+      <c r="C252" t="s">
+        <v>7</v>
+      </c>
+      <c r="D252" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>265</v>
+      </c>
+      <c r="B253" t="s">
+        <v>6</v>
+      </c>
+      <c r="C253" t="s">
+        <v>7</v>
+      </c>
+      <c r="D253" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>266</v>
+      </c>
+      <c r="B254" t="s">
+        <v>6</v>
+      </c>
+      <c r="C254" t="s">
+        <v>7</v>
+      </c>
+      <c r="D254" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>267</v>
+      </c>
+      <c r="B255" t="s">
+        <v>6</v>
+      </c>
+      <c r="C255" t="s">
+        <v>7</v>
+      </c>
+      <c r="D255" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>268</v>
+      </c>
+      <c r="B256" t="s">
+        <v>6</v>
+      </c>
+      <c r="C256" t="s">
+        <v>7</v>
+      </c>
+      <c r="D256" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>269</v>
+      </c>
+      <c r="B257" t="s">
+        <v>6</v>
+      </c>
+      <c r="C257" t="s">
+        <v>7</v>
+      </c>
+      <c r="D257" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>270</v>
+      </c>
+      <c r="B258" t="s">
+        <v>6</v>
+      </c>
+      <c r="C258" t="s">
+        <v>7</v>
+      </c>
+      <c r="D258" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>271</v>
+      </c>
+      <c r="B259" t="s">
+        <v>6</v>
+      </c>
+      <c r="C259" t="s">
+        <v>7</v>
+      </c>
+      <c r="D259" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>272</v>
+      </c>
+      <c r="B260" t="s">
+        <v>6</v>
+      </c>
+      <c r="C260" t="s">
+        <v>7</v>
+      </c>
+      <c r="D260" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>273</v>
+      </c>
+      <c r="B261" t="s">
+        <v>6</v>
+      </c>
+      <c r="C261" t="s">
+        <v>7</v>
+      </c>
+      <c r="D261" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>274</v>
+      </c>
+      <c r="B262" t="s">
+        <v>6</v>
+      </c>
+      <c r="C262" t="s">
+        <v>7</v>
+      </c>
+      <c r="D262" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>275</v>
+      </c>
+      <c r="B263" t="s">
+        <v>6</v>
+      </c>
+      <c r="C263" t="s">
+        <v>7</v>
+      </c>
+      <c r="D263" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>277</v>
+      </c>
+      <c r="B264" t="s">
+        <v>6</v>
+      </c>
+      <c r="C264" t="s">
+        <v>7</v>
+      </c>
+      <c r="D264" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>278</v>
+      </c>
+      <c r="B265" t="s">
+        <v>6</v>
+      </c>
+      <c r="C265" t="s">
+        <v>7</v>
+      </c>
+      <c r="D265" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>279</v>
+      </c>
+      <c r="B266" t="s">
+        <v>6</v>
+      </c>
+      <c r="C266" t="s">
+        <v>7</v>
+      </c>
+      <c r="D266" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>280</v>
+      </c>
+      <c r="B267" t="s">
+        <v>6</v>
+      </c>
+      <c r="C267" t="s">
+        <v>7</v>
+      </c>
+      <c r="D267" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>281</v>
+      </c>
+      <c r="B268" t="s">
+        <v>6</v>
+      </c>
+      <c r="C268" t="s">
+        <v>7</v>
+      </c>
+      <c r="D268" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>282</v>
+      </c>
+      <c r="B269" t="s">
+        <v>6</v>
+      </c>
+      <c r="C269" t="s">
+        <v>7</v>
+      </c>
+      <c r="D269" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>283</v>
+      </c>
+      <c r="B270" t="s">
+        <v>6</v>
+      </c>
+      <c r="C270" t="s">
+        <v>7</v>
+      </c>
+      <c r="D270" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>284</v>
+      </c>
+      <c r="B271" t="s">
+        <v>6</v>
+      </c>
+      <c r="C271" t="s">
+        <v>7</v>
+      </c>
+      <c r="D271" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>285</v>
+      </c>
+      <c r="B272" t="s">
+        <v>6</v>
+      </c>
+      <c r="C272" t="s">
+        <v>7</v>
+      </c>
+      <c r="D272" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>286</v>
+      </c>
+      <c r="B273" t="s">
+        <v>6</v>
+      </c>
+      <c r="C273" t="s">
+        <v>7</v>
+      </c>
+      <c r="D273" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>287</v>
+      </c>
+      <c r="B274" t="s">
+        <v>6</v>
+      </c>
+      <c r="C274" t="s">
+        <v>7</v>
+      </c>
+      <c r="D274" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>288</v>
+      </c>
+      <c r="B275" t="s">
+        <v>6</v>
+      </c>
+      <c r="C275" t="s">
+        <v>7</v>
+      </c>
+      <c r="D275" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>289</v>
+      </c>
+      <c r="B276" t="s">
+        <v>6</v>
+      </c>
+      <c r="C276" t="s">
+        <v>7</v>
+      </c>
+      <c r="D276" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>290</v>
+      </c>
+      <c r="B277" t="s">
+        <v>6</v>
+      </c>
+      <c r="C277" t="s">
+        <v>7</v>
+      </c>
+      <c r="D277" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>291</v>
+      </c>
+      <c r="B278" t="s">
+        <v>6</v>
+      </c>
+      <c r="C278" t="s">
+        <v>7</v>
+      </c>
+      <c r="D278" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>292</v>
+      </c>
+      <c r="B279" t="s">
+        <v>6</v>
+      </c>
+      <c r="C279" t="s">
+        <v>7</v>
+      </c>
+      <c r="D279" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>293</v>
+      </c>
+      <c r="B280" t="s">
+        <v>6</v>
+      </c>
+      <c r="C280" t="s">
+        <v>7</v>
+      </c>
+      <c r="D280" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>294</v>
+      </c>
+      <c r="B281" t="s">
+        <v>6</v>
+      </c>
+      <c r="C281" t="s">
+        <v>7</v>
+      </c>
+      <c r="D281" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>295</v>
+      </c>
+      <c r="B282" t="s">
+        <v>6</v>
+      </c>
+      <c r="C282" t="s">
+        <v>7</v>
+      </c>
+      <c r="D282" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>296</v>
+      </c>
+      <c r="B283" t="s">
+        <v>6</v>
+      </c>
+      <c r="C283" t="s">
+        <v>7</v>
+      </c>
+      <c r="D283" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>297</v>
+      </c>
+      <c r="B284" t="s">
+        <v>6</v>
+      </c>
+      <c r="C284" t="s">
+        <v>7</v>
+      </c>
+      <c r="D284" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>298</v>
+      </c>
+      <c r="B285" t="s">
+        <v>6</v>
+      </c>
+      <c r="C285" t="s">
+        <v>7</v>
+      </c>
+      <c r="D285" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>299</v>
+      </c>
+      <c r="B286" t="s">
+        <v>6</v>
+      </c>
+      <c r="C286" t="s">
+        <v>7</v>
+      </c>
+      <c r="D286" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>300</v>
+      </c>
+      <c r="B287" t="s">
+        <v>6</v>
+      </c>
+      <c r="C287" t="s">
+        <v>7</v>
+      </c>
+      <c r="D287" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>301</v>
+      </c>
+      <c r="B288" t="s">
+        <v>6</v>
+      </c>
+      <c r="C288" t="s">
+        <v>7</v>
+      </c>
+      <c r="D288" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>302</v>
+      </c>
+      <c r="B289" t="s">
+        <v>6</v>
+      </c>
+      <c r="C289" t="s">
+        <v>7</v>
+      </c>
+      <c r="D289" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>303</v>
+      </c>
+      <c r="B290" t="s">
+        <v>6</v>
+      </c>
+      <c r="C290" t="s">
+        <v>7</v>
+      </c>
+      <c r="D290" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>304</v>
+      </c>
+      <c r="B291" t="s">
+        <v>6</v>
+      </c>
+      <c r="C291" t="s">
+        <v>7</v>
+      </c>
+      <c r="D291" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>305</v>
+      </c>
+      <c r="B292" t="s">
+        <v>6</v>
+      </c>
+      <c r="C292" t="s">
+        <v>7</v>
+      </c>
+      <c r="D292" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>306</v>
+      </c>
+      <c r="B293" t="s">
+        <v>6</v>
+      </c>
+      <c r="C293" t="s">
+        <v>7</v>
+      </c>
+      <c r="D293" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>307</v>
+      </c>
+      <c r="B294" t="s">
+        <v>6</v>
+      </c>
+      <c r="C294" t="s">
+        <v>7</v>
+      </c>
+      <c r="D294" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>308</v>
+      </c>
+      <c r="B295" t="s">
+        <v>6</v>
+      </c>
+      <c r="C295" t="s">
+        <v>7</v>
+      </c>
+      <c r="D295" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>309</v>
+      </c>
+      <c r="B296" t="s">
+        <v>6</v>
+      </c>
+      <c r="C296" t="s">
+        <v>7</v>
+      </c>
+      <c r="D296" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>310</v>
+      </c>
+      <c r="B297" t="s">
+        <v>6</v>
+      </c>
+      <c r="C297" t="s">
+        <v>7</v>
+      </c>
+      <c r="D297" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>311</v>
+      </c>
+      <c r="B298" t="s">
+        <v>6</v>
+      </c>
+      <c r="C298" t="s">
+        <v>7</v>
+      </c>
+      <c r="D298" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>312</v>
+      </c>
+      <c r="B299" t="s">
+        <v>6</v>
+      </c>
+      <c r="C299" t="s">
+        <v>7</v>
+      </c>
+      <c r="D299" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>313</v>
+      </c>
+      <c r="B300" t="s">
+        <v>6</v>
+      </c>
+      <c r="C300" t="s">
+        <v>7</v>
+      </c>
+      <c r="D300" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>314</v>
+      </c>
+      <c r="B301" t="s">
+        <v>6</v>
+      </c>
+      <c r="C301" t="s">
+        <v>7</v>
+      </c>
+      <c r="D301" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>315</v>
+      </c>
+      <c r="B302" t="s">
+        <v>6</v>
+      </c>
+      <c r="C302" t="s">
+        <v>7</v>
+      </c>
+      <c r="D302" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>316</v>
+      </c>
+      <c r="B303" t="s">
+        <v>6</v>
+      </c>
+      <c r="C303" t="s">
+        <v>7</v>
+      </c>
+      <c r="D303" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>317</v>
+      </c>
+      <c r="B304" t="s">
+        <v>6</v>
+      </c>
+      <c r="C304" t="s">
+        <v>7</v>
+      </c>
+      <c r="D304" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>318</v>
+      </c>
+      <c r="B305" t="s">
+        <v>6</v>
+      </c>
+      <c r="C305" t="s">
+        <v>7</v>
+      </c>
+      <c r="D305" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>319</v>
+      </c>
+      <c r="B306" t="s">
+        <v>6</v>
+      </c>
+      <c r="C306" t="s">
+        <v>7</v>
+      </c>
+      <c r="D306" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>321</v>
+      </c>
+      <c r="B307" t="s">
+        <v>6</v>
+      </c>
+      <c r="C307" t="s">
+        <v>7</v>
+      </c>
+      <c r="D307" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>322</v>
+      </c>
+      <c r="B308" t="s">
+        <v>6</v>
+      </c>
+      <c r="C308" t="s">
+        <v>7</v>
+      </c>
+      <c r="D308" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>323</v>
+      </c>
+      <c r="B309" t="s">
+        <v>6</v>
+      </c>
+      <c r="C309" t="s">
+        <v>7</v>
+      </c>
+      <c r="D309" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>324</v>
+      </c>
+      <c r="B310" t="s">
+        <v>6</v>
+      </c>
+      <c r="C310" t="s">
+        <v>7</v>
+      </c>
+      <c r="D310" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>325</v>
+      </c>
+      <c r="B311" t="s">
+        <v>6</v>
+      </c>
+      <c r="C311" t="s">
+        <v>7</v>
+      </c>
+      <c r="D311" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>326</v>
+      </c>
+      <c r="B312" t="s">
+        <v>6</v>
+      </c>
+      <c r="C312" t="s">
+        <v>7</v>
+      </c>
+      <c r="D312" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>327</v>
+      </c>
+      <c r="B313" t="s">
+        <v>6</v>
+      </c>
+      <c r="C313" t="s">
+        <v>7</v>
+      </c>
+      <c r="D313" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>328</v>
+      </c>
+      <c r="B314" t="s">
+        <v>6</v>
+      </c>
+      <c r="C314" t="s">
+        <v>7</v>
+      </c>
+      <c r="D314" t="s">
+        <v>320</v>
       </c>
     </row>
   </sheetData>

--- a/input/products.xlsx
+++ b/input/products.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
   <si>
     <t>url</t>
   </si>
@@ -28,7 +28,7 @@
     <t>error</t>
   </si>
   <si>
-    <t>https://www.tatacliq.com/renee-natural-makeup-fixer-75-ml/p-mp000000027720317</t>
+    <t>https://www.vijaysales.com/p/191494/ifb-20-ltrs-convection-microwave-20pm-mec2-white</t>
   </si>
   <si>
     <t/>
@@ -37,16 +37,13 @@
     <t>done</t>
   </si>
   <si>
-    <t>2026-09-17T09:31:01.769Z</t>
-  </si>
-  <si>
-    <t>https://www.tatacliq.com/pac-micro-finish-makeup-fixer-120-ml/p-mp000000015561989</t>
-  </si>
-  <si>
-    <t>https://www.tatacliq.com/lakme-makeup-skincare-vit-c-superglow-skin-perfecting-makeup-fixer-60-ml/p-mp000000022501402</t>
-  </si>
-  <si>
-    <t>https://www.tatacliq.com/daily-life-forever52-all-day-long-makeup-fixer-100-ml/p-mp000000025883622</t>
+    <t>2026-09-18T05:37:04.759Z</t>
+  </si>
+  <si>
+    <t>https://www.vijaysales.com/p/109229/lg-20-ltrs-solo-microwave-ms2043db-black</t>
+  </si>
+  <si>
+    <t>https://www.vijaysales.com/p/224298/morphy-richards-29-litres-rcad-digi-oven-toaster-griller-with-13-preset-menu-digital-display-ai-preset-menu-knob-control-deep-blue</t>
   </si>
 </sst>
 </file>
@@ -423,7 +420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
@@ -490,20 +487,6 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/input/products.xlsx
+++ b/input/products.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="60">
   <si>
     <t>url</t>
   </si>
@@ -28,7 +28,7 @@
     <t>error</t>
   </si>
   <si>
-    <t>https://www.vijaysales.com/p/191494/ifb-20-ltrs-convection-microwave-20pm-mec2-white</t>
+    <t>https://www.myntra.com/tshirts/wrogn/wrogn-pure-cotton-striped-polo-collar-slim-fit-t-shirt/26531622/buy</t>
   </si>
   <si>
     <t/>
@@ -37,13 +37,160 @@
     <t>done</t>
   </si>
   <si>
-    <t>2026-09-18T05:37:04.759Z</t>
-  </si>
-  <si>
-    <t>https://www.vijaysales.com/p/109229/lg-20-ltrs-solo-microwave-ms2043db-black</t>
-  </si>
-  <si>
-    <t>https://www.vijaysales.com/p/224298/morphy-richards-29-litres-rcad-digi-oven-toaster-griller-with-13-preset-menu-digital-display-ai-preset-menu-knob-control-deep-blue</t>
+    <t>2026-09-25T04:00:44.965Z</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/french+connection/french-connection-men-striped-polo-collar-pure-cotton-t-shirt/21388860/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/lounge-tshirts/levis/levis-men-soft-pure-cotton-round-neck-half-sleeve-tshirt/12027436/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/lounge-tshirts/levis/levis-men-soft-pure-cotton-round-neck-half-sleeve-tshirt/12027432/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/adidas/adidas-men-printed-pure-cotton-t-shirt/34149996/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/lounge-tshirts/pepe+jeans/pepe-jeans-men-crew-neck-relaxed-fit-lounge-tshirt/33353185/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/roadsail/roadsail-men-scuderia-ferrari-formula-1-printed-drop-shoulder-sleeves-t-shirt/45728425/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/prosharx/prosharx-men-colourblocked-compression-t-shirt/44993306/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/lounge-tshirts/levis/levis-men-soft-pure-cotton-round-neck-half-sleeve-tshirt/12027422/buy</t>
+  </si>
+  <si>
+    <t>2026-09-25T04:00:44.966Z</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/lounge-tshirts/u.s.+polo+assn./us-polo-assn-men-embroidered-logo-pure-cotton-lightweight-lounge-t-shirt/22492582/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/bene+kleed/bene-kleed-men-regular-fit-embroidered-t-shirt/41737229/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/oishee/oishee-unisex-striped-t-shirt/46425378/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/here%26now/herenow-men-colourblocked-polo-collar-t-shirt/46222266/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/hrx+by+hrithik+roshan/hrx-by-hrithik-roshan-men-printed-running-rapid-dry-t-shirt/29010960/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/lounge-tshirts/damensch/damensch-ultralight-basic-crew-pure-cotton-lounge-t-shirts/30205303/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/lounge-tshirts/levis/levis-men-soft-pure-cotton-round-neck-half-sleeve-tshirt/12027418/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/kook+n+keech/kook-n-keech-drop-shoulder-sleeves-oversized-pure-cotton-t-shirt/27506790/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/lounge-tshirts/xyxx/xyxx-men-pace-intellieaze-cotton-t-shirt/24026378/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/hrx+by+hrithik+roshan/hrx-by-hrithik-roshan-men-colourblocked-t-shirt/44709936/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/prosharx/prosharx-men-brand-logo-dri-fit-compression-t-shirt/44591460/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/cahoot/cahoot-men-solid-polo-collar-cotton-t-shirt/32193183/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/lounge-tshirts/pepe+jeans/pepe-jeans-men-crew-neck-relaxed-fit-lounge-tshirt/32762106/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/imsa+moda/imsa-moda-men-colourblocked-t-shirt/46258981/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/lounge-tshirts/van+heusen+innerwear/van-heusen-men-cotton-crew-neck-solid-regular-fit-short-sleeves-lounge-tshirt/30104756/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/the+modvue/the-modvue-men-brand-logo-dyed-t-shirt/45812329/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/the+indian+garage+co/the-indian-garage-co-men-t-shirt/40199466/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/lounge-tshirts/damensch/damensch-ultralight-basic-crew-pure-cotton-lounge-t-shirts/30205304/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/cahoot/cahoot-men-self-design-polo-collar-cotton-t-shirt/32193190/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/prosharx/prosharx-men-brand-logo-dri-fit-compression-t-shirt/41918326/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/lounge-tshirts/u.s.+polo+assn./us-polo-assn-men-pure-cotton-comfort-fit-lounge-t-shirt/36468833/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/v-mart/v-mart-men-polo-collar-slim-fit-t-shirt/46155716/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/hrx+by+hrithik+roshan/hrx-by-hrithik-roshan-men-brand-logo-printed-t-shirt/41509398/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/lounge-tshirts/van+heusen+innerwear/van-heusen-innerwear-cotton-crew-neck-regular-short-sleeves-soft-breathable-lounge-tshirt/29638056/buy</t>
+  </si>
+  <si>
+    <t>2026-09-25T04:00:44.967Z</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/lounge-tshirts/damensch/damensch-neo-cool-pure-cotton-regular-fit-tank-lounge-t-shirt/19563322/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/glitchez/glitchez-printed-oversized-fit-t-shirt/31819294/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/cahoot/cahoot-men-self-design-polo-collar-cotton-t-shirt/32193132/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/hotfits/hotfits-men-typography-printed-organic-cotton-t-shirt/46315858/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts-smart/urban+trees/urban-trees-printed-cotton-round-neck-tshirts/42543341/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/lounge-tshirts/pepe+jeans/pepe-jeans-men-crew-neck-relaxed-fit-lounge-tshirt/32762104/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/lounge-tshirts/damensch/damensch-men-ultralight-basic-crew-pure-cotton-lounge-t-shirts/30205305/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/gap/gap-brand-logo-printed-pure-cotton-slim-fit-t-shirt/40934832/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/lounge-tshirts/pepe+jeans/pepe-jeans-round-neck-cotton-t-shirt/34851621/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/teevybe/teevybe-men-typography-printed-t-shirt/46330752/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/adidas/adidas-3-stripes-pure-cotton-t-shirt/35840598/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/lounge-tshirts/van+heusen+innerwear/van-heusen-innerwear-cotton-crew-neck-solid--short-sleeves-soft-breathable-lounge-tshirts/29638088/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/bdsquare/bdsquare-men-drop-shoulder-sleeves-t-shirt/39825768/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/nostrum/nostrum-men-solid-polo-collar-regular-fit-half-sleeve-t-shirt/33617040/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/flying+machine/flying-machine-pure-cotton-relaxed-fit-t-shirt/31598705/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/roadster/roadster-men-ready-to-wear-short-sleeves-typography-printed-t-shirt/46383516/buy</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/mast+%26+harbour/mast--harbour-men-oversized-printed-t-shirt/45606383/buy</t>
   </si>
 </sst>
 </file>
@@ -420,7 +567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
@@ -487,6 +634,664 @@
         <v>8</v>
       </c>
     </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/input/products.xlsx
+++ b/input/products.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="59">
   <si>
     <t>url</t>
   </si>
@@ -37,7 +37,7 @@
     <t>done</t>
   </si>
   <si>
-    <t>2026-09-25T04:00:44.965Z</t>
+    <t>2026-09-25T11:52:31.380Z</t>
   </si>
   <si>
     <t>https://www.myntra.com/tshirts/french+connection/french-connection-men-striped-polo-collar-pure-cotton-t-shirt/21388860/buy</t>
@@ -64,9 +64,6 @@
     <t>https://www.myntra.com/lounge-tshirts/levis/levis-men-soft-pure-cotton-round-neck-half-sleeve-tshirt/12027422/buy</t>
   </si>
   <si>
-    <t>2026-09-25T04:00:44.966Z</t>
-  </si>
-  <si>
     <t>https://www.myntra.com/lounge-tshirts/u.s.+polo+assn./us-polo-assn-men-embroidered-logo-pure-cotton-lightweight-lounge-t-shirt/22492582/buy</t>
   </si>
   <si>
@@ -139,10 +136,10 @@
     <t>https://www.myntra.com/lounge-tshirts/van+heusen+innerwear/van-heusen-innerwear-cotton-crew-neck-regular-short-sleeves-soft-breathable-lounge-tshirt/29638056/buy</t>
   </si>
   <si>
-    <t>2026-09-25T04:00:44.967Z</t>
-  </si>
-  <si>
     <t>https://www.myntra.com/lounge-tshirts/damensch/damensch-neo-cool-pure-cotton-regular-fit-tank-lounge-t-shirt/19563322/buy</t>
+  </si>
+  <si>
+    <t>2026-09-25T11:52:31.381Z</t>
   </si>
   <si>
     <t>https://www.myntra.com/tshirts/glitchez/glitchez-printed-oversized-fit-t-shirt/31819294/buy</t>
@@ -715,12 +712,12 @@
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
         <v>6</v>
@@ -729,12 +726,12 @@
         <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
         <v>6</v>
@@ -743,12 +740,12 @@
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
         <v>6</v>
@@ -757,12 +754,12 @@
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
         <v>6</v>
@@ -771,12 +768,12 @@
         <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
         <v>6</v>
@@ -785,12 +782,12 @@
         <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
         <v>6</v>
@@ -799,12 +796,12 @@
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
         <v>6</v>
@@ -813,12 +810,12 @@
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
         <v>6</v>
@@ -827,12 +824,12 @@
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" t="s">
         <v>6</v>
@@ -841,12 +838,12 @@
         <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" t="s">
         <v>6</v>
@@ -855,12 +852,12 @@
         <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" t="s">
         <v>6</v>
@@ -869,12 +866,12 @@
         <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" t="s">
         <v>6</v>
@@ -883,12 +880,12 @@
         <v>7</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" t="s">
         <v>6</v>
@@ -897,12 +894,12 @@
         <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" t="s">
         <v>6</v>
@@ -911,12 +908,12 @@
         <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
         <v>6</v>
@@ -925,12 +922,12 @@
         <v>7</v>
       </c>
       <c r="D25" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" t="s">
         <v>6</v>
@@ -939,12 +936,12 @@
         <v>7</v>
       </c>
       <c r="D26" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" t="s">
         <v>6</v>
@@ -953,12 +950,12 @@
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" t="s">
         <v>6</v>
@@ -967,12 +964,12 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" t="s">
         <v>6</v>
@@ -981,12 +978,12 @@
         <v>7</v>
       </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" t="s">
         <v>6</v>
@@ -995,12 +992,12 @@
         <v>7</v>
       </c>
       <c r="D30" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" t="s">
         <v>6</v>
@@ -1009,12 +1006,12 @@
         <v>7</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" t="s">
         <v>6</v>
@@ -1023,12 +1020,12 @@
         <v>7</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" t="s">
         <v>6</v>
@@ -1037,12 +1034,12 @@
         <v>7</v>
       </c>
       <c r="D33" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" t="s">
         <v>6</v>
@@ -1051,12 +1048,12 @@
         <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B35" t="s">
         <v>6</v>
@@ -1070,7 +1067,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B36" t="s">
         <v>6</v>
@@ -1084,7 +1081,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B37" t="s">
         <v>6</v>
@@ -1098,7 +1095,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B38" t="s">
         <v>6</v>
@@ -1112,7 +1109,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
         <v>6</v>
@@ -1126,7 +1123,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B40" t="s">
         <v>6</v>
@@ -1140,7 +1137,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B41" t="s">
         <v>6</v>
@@ -1154,7 +1151,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B42" t="s">
         <v>6</v>
@@ -1168,7 +1165,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B43" t="s">
         <v>6</v>
@@ -1182,7 +1179,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B44" t="s">
         <v>6</v>
@@ -1196,7 +1193,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B45" t="s">
         <v>6</v>
@@ -1210,7 +1207,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B46" t="s">
         <v>6</v>
@@ -1224,7 +1221,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B47" t="s">
         <v>6</v>
@@ -1238,7 +1235,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B48" t="s">
         <v>6</v>
@@ -1252,7 +1249,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B49" t="s">
         <v>6</v>
@@ -1266,7 +1263,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B50" t="s">
         <v>6</v>
@@ -1280,7 +1277,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B51" t="s">
         <v>6</v>
